--- a/data/trending_integrated_20261007_10.xlsx
+++ b/data/trending_integrated_20261007_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z13"/>
+  <dimension ref="A1:Z14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>제이앤티씨</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5360</v>
+        <v>27300</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+21.82%</t>
+          <t>'+18.95%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3.32</v>
+        <v>0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F2" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G2" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="H2" t="n">
-        <v>4.72</v>
+        <v>2.82</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>4400</v>
+        <v>22950</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>26200</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>27600</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>25550</v>
       </c>
       <c r="N2" t="n">
-        <v>1.4</v>
+        <v>2.42</v>
       </c>
       <c r="O2" t="n">
-        <v>142342000000</v>
+        <v>70886466925</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>30100</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>11140</v>
       </c>
       <c r="R2" t="n">
-        <v>1405000</v>
+        <v>158000</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-205000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>빛과전자, 기타법인 자사주 매집 및 JP모건 매수세 확인. 2200억 규모 수주 계약 기대감 있으나 공시 지연.</t>
+          <t>유리 기판 관련 긍정적 전망 및 2천억 규모의 주포 존재 언급. 브로드컴, 인텔 돌파 가능성과 함께 급등 기대감 고조.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['자사주매집', '수주계약', 'JP모건']</t>
+          <t>['유리 기판', '주포', '급등 기대']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>204270</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>제이앤티씨</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26750</v>
+        <v>17300</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.56%</t>
+          <t>'+16.34%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4</v>
+        <v>0.98</v>
       </c>
       <c r="E3" t="n">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="F3" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="H3" t="n">
-        <v>2.82</v>
+        <v>2.37</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>22950</v>
+        <v>14870</v>
       </c>
       <c r="K3" t="n">
-        <v>26200</v>
+        <v>15480</v>
       </c>
       <c r="L3" t="n">
-        <v>27600</v>
+        <v>17320</v>
       </c>
       <c r="M3" t="n">
-        <v>25550</v>
+        <v>14600</v>
       </c>
       <c r="N3" t="n">
-        <v>2.42</v>
+        <v>1.39</v>
       </c>
       <c r="O3" t="n">
-        <v>62698986325</v>
+        <v>145313063935</v>
       </c>
       <c r="P3" t="n">
-        <v>30100</v>
+        <v>17320</v>
       </c>
       <c r="Q3" t="n">
-        <v>11140</v>
+        <v>6320</v>
       </c>
       <c r="R3" t="n">
-        <v>158000</v>
+        <v>-91000</v>
       </c>
       <c r="S3" t="n">
-        <v>-205000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>제이앤티씨, 유상증자 이슈에도 주가 상승 기대감. 2천억 규모 주포 활동 및 유리 기판 사업 관련 언급.</t>
+          <t>개인정보 유출 및 보안 사고 증가로 인한 보안주 상승세. 라온의 양자보안 공급 논의 및 기타 법인 자사주 매집 사실 언급. 주가 급등 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['유상증자', '주포', '유리기판']</t>
+          <t>['개인정보 유출', '양자보안', '자사주 매집']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10370</v>
+        <v>10510</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.24%</t>
+          <t>'+8.69%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H4" t="n">
         <v>5.01</v>
@@ -794,7 +794,7 @@
         <v>4.84</v>
       </c>
       <c r="O4" t="n">
-        <v>10907854510</v>
+        <v>11281047025</v>
       </c>
       <c r="P4" t="n">
         <v>15900</v>
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15850</v>
+        <v>5395</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.59%</t>
+          <t>'+7.68%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.98</v>
+        <v>3.32</v>
       </c>
       <c r="E5" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F5" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G5" t="n">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="H5" t="n">
-        <v>2.37</v>
+        <v>4.72</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>14870</v>
+        <v>5010</v>
       </c>
       <c r="K5" t="n">
-        <v>15480</v>
+        <v>5120</v>
       </c>
       <c r="L5" t="n">
-        <v>16960</v>
+        <v>5990</v>
       </c>
       <c r="M5" t="n">
-        <v>14600</v>
+        <v>4950</v>
       </c>
       <c r="N5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="O5" t="n">
-        <v>122557985870</v>
+        <v>148445737225</v>
       </c>
       <c r="P5" t="n">
-        <v>16960</v>
+        <v>8100</v>
       </c>
       <c r="Q5" t="n">
-        <v>6320</v>
+        <v>592</v>
       </c>
       <c r="R5" t="n">
-        <v>-91000</v>
+        <v>1405000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>라온시큐어, 개인정보 유출 사고 발생 및 미국 보안주 상승 수혜 기대. 양자보안 기술 공급 논의 및 주포 물량 보유 확인.</t>
+          <t>기타법인의 자사주 매집과 2200억 규모의 수주 계약 공시 가능성 언급. 미국 증시 호조 및 급등 기대감 표출.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['정보보안', '양자보안', '주포']</t>
+          <t>['자사주 매집', '수주 계약', '급등 기대']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>276000</v>
+        <v>243500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.47%</t>
+          <t>'+1.04%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="E6" t="n">
-        <v>739</v>
+        <v>125</v>
       </c>
       <c r="F6" t="n">
-        <v>452</v>
+        <v>85</v>
       </c>
       <c r="G6" t="n">
-        <v>2232</v>
+        <v>610</v>
       </c>
       <c r="H6" t="n">
-        <v>46.37</v>
+        <v>4.12</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>272000</v>
+        <v>241000</v>
       </c>
       <c r="K6" t="n">
-        <v>269500</v>
+        <v>253000</v>
       </c>
       <c r="L6" t="n">
-        <v>279500</v>
+        <v>257000</v>
       </c>
       <c r="M6" t="n">
-        <v>268500</v>
+        <v>235000</v>
       </c>
       <c r="N6" t="n">
-        <v>46.41</v>
+        <v>4.08</v>
       </c>
       <c r="O6" t="n">
-        <v>1381316081250</v>
+        <v>64123040000</v>
       </c>
       <c r="P6" t="n">
-        <v>374500</v>
+        <v>1233000</v>
       </c>
       <c r="Q6" t="n">
-        <v>90200</v>
+        <v>120000</v>
       </c>
       <c r="R6" t="n">
-        <v>1232000</v>
+        <v>-43000</v>
       </c>
       <c r="S6" t="n">
-        <v>-121000</v>
+        <v>2000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>정치적 이슈와 거시 경제 불확실성이 혼재하며, 단기적인 하락 가능성이 제기됨.</t>
+          <t>경구용 인슐린 10조원대 L/O 예상 및 캐나다/독일 건 관련 긍정적 전망. 외국인 수급 개선 및 거래량 증가 추세 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['자사주 매입', '환율', '실적 발표']</t>
+          <t>['경구용 인슐린', 'L/O 예상', '외국인 수급']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>81800</v>
+        <v>274000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.37%</t>
+          <t>'+0.74%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>189</v>
+        <v>797</v>
       </c>
       <c r="F7" t="n">
-        <v>118</v>
+        <v>476</v>
       </c>
       <c r="G7" t="n">
-        <v>521</v>
+        <v>2355</v>
       </c>
       <c r="H7" t="n">
-        <v>22.59</v>
+        <v>46.37</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>81500</v>
+        <v>272000</v>
       </c>
       <c r="K7" t="n">
-        <v>83500</v>
+        <v>269500</v>
       </c>
       <c r="L7" t="n">
-        <v>84300</v>
+        <v>279500</v>
       </c>
       <c r="M7" t="n">
-        <v>81700</v>
+        <v>268500</v>
       </c>
       <c r="N7" t="n">
-        <v>22.56</v>
+        <v>46.41</v>
       </c>
       <c r="O7" t="n">
-        <v>82511872700</v>
+        <v>1583807903250</v>
       </c>
       <c r="P7" t="n">
-        <v>139200</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>57000</v>
+        <v>90200</v>
       </c>
       <c r="R7" t="n">
-        <v>72000</v>
+        <v>1232000</v>
       </c>
       <c r="S7" t="n">
-        <v>-40000</v>
+        <v>-121000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 원전주 급등에 따른 기대감, 구글 계약 호재 언급.</t>
+          <t>게시글에서 언급된 정치적, 사회적 이슈와는 무관하게 주가 및 투자 심리에 대한 구체적인 사실 기반 분석은 부재함.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['원전', '구글 계약']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,86 +1108,86 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>241000</v>
+        <v>81600</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E8" t="n">
+        <v>200</v>
+      </c>
+      <c r="F8" t="n">
         <v>120</v>
       </c>
-      <c r="F8" t="n">
-        <v>81</v>
-      </c>
       <c r="G8" t="n">
-        <v>588</v>
+        <v>525</v>
       </c>
       <c r="H8" t="n">
-        <v>4.12</v>
+        <v>22.59</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>241000</v>
+        <v>81500</v>
       </c>
       <c r="K8" t="n">
-        <v>253000</v>
+        <v>83500</v>
       </c>
       <c r="L8" t="n">
-        <v>257000</v>
+        <v>84300</v>
       </c>
       <c r="M8" t="n">
-        <v>235000</v>
+        <v>81500</v>
       </c>
       <c r="N8" t="n">
-        <v>4.08</v>
+        <v>22.56</v>
       </c>
       <c r="O8" t="n">
-        <v>60380057500</v>
+        <v>85543086050</v>
       </c>
       <c r="P8" t="n">
-        <v>1233000</v>
+        <v>139200</v>
       </c>
       <c r="Q8" t="n">
-        <v>120000</v>
+        <v>57000</v>
       </c>
       <c r="R8" t="n">
-        <v>-43000</v>
+        <v>72000</v>
       </c>
       <c r="S8" t="n">
-        <v>2000</v>
+        <v>-40000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>경구용 인슐린 10조원대 L/O 예상 및 캐나다/독일 관련 호재 기대감. 다만, 외국인 수급 및 거래량 실림 등 일부 팩트 기반 언급 존재.</t>
+          <t>미국 원전주 급등에 따른 기대감, 구글 계약 호재 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['경구용 인슐린', '공매도', 'L/O']</t>
+          <t>['원전', '구글 계약']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,77 +1200,77 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18420</v>
+        <v>17630</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.59%</t>
+          <t>'-0.68%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.11</v>
+        <v>0.11</v>
       </c>
       <c r="E9" t="n">
-        <v>103</v>
+        <v>41</v>
       </c>
       <c r="F9" t="n">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="G9" t="n">
-        <v>624</v>
+        <v>193</v>
       </c>
       <c r="H9" t="n">
-        <v>4.92</v>
+        <v>9.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>18530</v>
+        <v>17750</v>
       </c>
       <c r="K9" t="n">
-        <v>18950</v>
+        <v>17970</v>
       </c>
       <c r="L9" t="n">
-        <v>19870</v>
+        <v>18030</v>
       </c>
       <c r="M9" t="n">
-        <v>18360</v>
+        <v>17610</v>
       </c>
       <c r="N9" t="n">
-        <v>3.81</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>210048375205</v>
+        <v>28099504315</v>
       </c>
       <c r="P9" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q9" t="n">
-        <v>1272</v>
+        <v>3320</v>
       </c>
       <c r="R9" t="n">
-        <v>-317000</v>
+        <v>-95000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-29000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>대한광통신, 미국 광통신 주가 상승 및 젠슨 황의 광통신 지지 영향. 신고가 모멘텀 기대감 있으나, 구체적인 호재는 미확인.</t>
+          <t>올해 수주 목표 언급 및 미국 원전 건설 분위기 긍정적 전망 제시. 다만, 주가 상승에 대한 기대와 달리 실제 움직임은 지연되며, 일부 부정적 의견도 혼재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', '신고가', '모멘텀']</t>
+          <t>['수주 목표', '원전 건설', '주가 전망']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1760000</v>
+        <v>1756000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.73%</t>
+          <t>'-0.96%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>459</v>
       </c>
       <c r="G10" t="n">
-        <v>2069</v>
+        <v>2042</v>
       </c>
       <c r="H10" t="n">
         <v>49.71</v>
@@ -1346,7 +1346,7 @@
         <v>49.76</v>
       </c>
       <c r="O10" t="n">
-        <v>1442045080000</v>
+        <v>1553763023500</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>SK하이닉스, ADR 급락 및 락업 해제 이슈로 인한 주가 하락 우려. 외국인 매도세 지속, 실적 대비 주가 부진.</t>
+          <t>SK하이닉스 ADR 급락 및 락업 해제 관련 부정적 뉴스 다수 언급. 실적 호조에도 불구하고 외국인 매도에 대한 의문 제기.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['ADR', '락업해제', '외국인매도']</t>
+          <t>['SK하이닉스 ADR', '락업 해제', '외국인 매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>46050</v>
+        <v>18250</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.85%</t>
+          <t>'-1.51%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.02</v>
+        <v>1.11</v>
       </c>
       <c r="E11" t="n">
-        <v>216</v>
+        <v>108</v>
       </c>
       <c r="F11" t="n">
-        <v>144</v>
+        <v>83</v>
       </c>
       <c r="G11" t="n">
-        <v>1449</v>
+        <v>651</v>
       </c>
       <c r="H11" t="n">
-        <v>14.12</v>
+        <v>4.92</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>47400</v>
+        <v>18530</v>
       </c>
       <c r="K11" t="n">
-        <v>46350</v>
+        <v>18950</v>
       </c>
       <c r="L11" t="n">
-        <v>47850</v>
+        <v>19870</v>
       </c>
       <c r="M11" t="n">
-        <v>45650</v>
+        <v>18220</v>
       </c>
       <c r="N11" t="n">
-        <v>14.1</v>
+        <v>3.81</v>
       </c>
       <c r="O11" t="n">
-        <v>25048058425</v>
+        <v>221041941240</v>
       </c>
       <c r="P11" t="n">
-        <v>69200</v>
+        <v>31500</v>
       </c>
       <c r="Q11" t="n">
-        <v>24150</v>
+        <v>1272</v>
       </c>
       <c r="R11" t="n">
-        <v>5000</v>
+        <v>-317000</v>
       </c>
       <c r="S11" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>FDA 승인 가능성 90% 이상에 기반한 높은 기대감. 공매도 세력과의 공방 속에 대규모 매출 전망.</t>
+          <t>미국 광통신 주가 상승 및 젠슨 황의 광통신 지지 언급. 19,000원 안착 및 25,000원 돌파 기대감 나타남.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['FDA 승인', '공매도', '매출 전망']</t>
+          <t>['광통신', '미국 주가', '젠슨 황']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30500</v>
+        <v>46050</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.94%</t>
+          <t>'-2.85%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>66</v>
+        <v>228</v>
       </c>
       <c r="F12" t="n">
-        <v>42</v>
+        <v>147</v>
       </c>
       <c r="G12" t="n">
-        <v>148</v>
+        <v>1495</v>
       </c>
       <c r="H12" t="n">
-        <v>10.78</v>
+        <v>14.12</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>31750</v>
+        <v>47400</v>
       </c>
       <c r="K12" t="n">
-        <v>32600</v>
+        <v>46350</v>
       </c>
       <c r="L12" t="n">
-        <v>32850</v>
+        <v>47850</v>
       </c>
       <c r="M12" t="n">
-        <v>30500</v>
+        <v>45650</v>
       </c>
       <c r="N12" t="n">
-        <v>10.77</v>
+        <v>14.1</v>
       </c>
       <c r="O12" t="n">
-        <v>60293184125</v>
+        <v>26033353950</v>
       </c>
       <c r="P12" t="n">
-        <v>75900</v>
+        <v>69200</v>
       </c>
       <c r="Q12" t="n">
-        <v>15960</v>
+        <v>24150</v>
       </c>
       <c r="R12" t="n">
-        <v>-379000</v>
+        <v>5000</v>
       </c>
       <c r="S12" t="n">
-        <v>-21000</v>
+        <v>2000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>경쟁사 대비 부진한 주가 흐름 및 주식 관리 부재에 대한 불만 토로. 기관/외인 매도세 확인.</t>
+          <t>FDA 승인 가능성 90% 이상 언급 및 시총 100조원 목표 제시. 공매도 세력에 대한 비판과 함께 대세 우상향 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['가온전선', '주가 관리', '기관 매도']</t>
+          <t>['FDA 승인', '공매도', '대세 우상향']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,97 +1568,189 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12450</v>
+        <v>30550</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.30%</t>
+          <t>'-3.78%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.88</v>
+        <v>0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="F13" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G13" t="n">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="H13" t="n">
-        <v>1.42</v>
+        <v>10.78</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>13010</v>
+        <v>31750</v>
       </c>
       <c r="K13" t="n">
-        <v>12330</v>
+        <v>32600</v>
       </c>
       <c r="L13" t="n">
-        <v>13560</v>
+        <v>32850</v>
       </c>
       <c r="M13" t="n">
-        <v>12260</v>
+        <v>30500</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>10.77</v>
       </c>
       <c r="O13" t="n">
-        <v>29116722960</v>
+        <v>62536949175</v>
       </c>
       <c r="P13" t="n">
-        <v>22250</v>
+        <v>75900</v>
       </c>
       <c r="Q13" t="n">
-        <v>6000</v>
+        <v>15960</v>
       </c>
       <c r="R13" t="n">
-        <v>-100000</v>
+        <v>-379000</v>
       </c>
       <c r="S13" t="n">
-        <v>3000</v>
+        <v>-21000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>유상증자 및 신규 상장 물량 부담으로 인한 하락세. 주가 조작 의혹 제기.</t>
+          <t>가온전선과의 비교를 통해 부진한 실적과 주가 흐름을 지적하며, 회사 내부 문제 및 주식 관리 부실에 대한 우려 제기. 일부 수주 건 언급 있으나 영향력 미미.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['유상증자', '신규 상장', '주가 조작']</t>
+          <t>['가온전선', '주가 관리', '수주']</t>
         </is>
       </c>
       <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>001440</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HLB제약</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>12500</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>'-3.92%</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="E14" t="n">
+        <v>62</v>
+      </c>
+      <c r="F14" t="n">
+        <v>51</v>
+      </c>
+      <c r="G14" t="n">
+        <v>137</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>13010</v>
+      </c>
+      <c r="K14" t="n">
+        <v>12330</v>
+      </c>
+      <c r="L14" t="n">
+        <v>13560</v>
+      </c>
+      <c r="M14" t="n">
+        <v>12260</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>29744502725</v>
+      </c>
+      <c r="P14" t="n">
+        <v>22250</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>6000</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>기타법인의 대량 자사주 매집과 유증 물량 출회 속에서 투자자들의 혼란과 경계심이 공존하고 있다. 일부는 호재 대기 및 매수 기회로 보고 있으나, 주가 조작 의혹 및 상장 물량 부담에 대한 우려도 제기된다.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>['자사주 매집', '유증 물량', '주가 조작']</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
         <v>2</v>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>047920</t>
         </is>

--- a/data/trending_integrated_20261007_10.xlsx
+++ b/data/trending_integrated_20261007_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27300</v>
+        <v>26800</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+18.95%</t>
+          <t>'+16.78%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F2" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G2" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="H2" t="n">
         <v>2.82</v>
@@ -610,7 +610,7 @@
         <v>2.42</v>
       </c>
       <c r="O2" t="n">
-        <v>70886466925</v>
+        <v>75345058500</v>
       </c>
       <c r="P2" t="n">
         <v>30100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>유리 기판 관련 긍정적 전망 및 2천억 규모의 주포 존재 언급. 브로드컴, 인텔 돌파 가능성과 함께 급등 기대감 고조.</t>
+          <t>유증 관련 논쟁 속 유리 기술력에 대한 기대감 존재. 브로드컴, 인텔 돌파 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['유리 기판', '주포', '급등 기대']</t>
+          <t>['유증', '유리기술력', '주포']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17300</v>
+        <v>17130</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.34%</t>
+          <t>'+15.20%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.98</v>
       </c>
       <c r="E3" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G3" t="n">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H3" t="n">
         <v>2.37</v>
@@ -693,7 +693,7 @@
         <v>15480</v>
       </c>
       <c r="L3" t="n">
-        <v>17320</v>
+        <v>17590</v>
       </c>
       <c r="M3" t="n">
         <v>14600</v>
@@ -702,10 +702,10 @@
         <v>1.39</v>
       </c>
       <c r="O3" t="n">
-        <v>145313063935</v>
+        <v>172966034555</v>
       </c>
       <c r="P3" t="n">
-        <v>17320</v>
+        <v>17590</v>
       </c>
       <c r="Q3" t="n">
         <v>6320</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>개인정보 유출 및 보안 사고 증가로 인한 보안주 상승세. 라온의 양자보안 공급 논의 및 기타 법인 자사주 매집 사실 언급. 주가 급등 기대.</t>
+          <t>개인정보 유출 및 해킹 사고 증가로 인한 보안 투자 확대 기대감. 농협, KDB생명 등 해킹 방어 이력 및 양자보안 공급 논의 언급. 보안 0티어 대장주로 신고가 돌파.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['개인정보 유출', '양자보안', '자사주 매집']</t>
+          <t>['보안', '개인정보 유출', '양자보안']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,79 +747,79 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10510</v>
+        <v>7530</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.69%</t>
+          <t>'+11.56%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.17</v>
+        <v>-0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="F4" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="G4" t="n">
-        <v>238</v>
+        <v>81</v>
       </c>
       <c r="H4" t="n">
-        <v>5.01</v>
+        <v>5.12</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>9670</v>
+        <v>6750</v>
       </c>
       <c r="K4" t="n">
-        <v>11020</v>
+        <v>6710</v>
       </c>
       <c r="L4" t="n">
-        <v>11030</v>
+        <v>8310</v>
       </c>
       <c r="M4" t="n">
-        <v>10300</v>
+        <v>6690</v>
       </c>
       <c r="N4" t="n">
-        <v>4.84</v>
+        <v>5.14</v>
       </c>
       <c r="O4" t="n">
-        <v>11281047025</v>
+        <v>39614985300</v>
       </c>
       <c r="P4" t="n">
-        <v>15900</v>
+        <v>23500</v>
       </c>
       <c r="Q4" t="n">
-        <v>6310</v>
+        <v>2890</v>
       </c>
       <c r="R4" t="n">
-        <v>-216000</v>
+        <v>-226000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>신풍제약, 페스트·에볼라 등 다양한 질병 테마주로 언급되며 투자 심리 자극. 모건스탠리 매수세 확인되나, 실질적 근거 부족.</t>
+          <t>정부의 용적률 상향 및 그린벨트 해제 기대감 속 건설 기초 소재 대장주로서 목표가 10만원 이상 제시. 외국인 프로그램 매수세 확인.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['테마주', '백신', '질병']</t>
+          <t>['건설 기초 소재', '용적률 상향', '외국인 매수']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5395</v>
+        <v>5470</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.68%</t>
+          <t>'+9.18%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>3.32</v>
       </c>
       <c r="E5" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G5" t="n">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="H5" t="n">
         <v>4.72</v>
@@ -886,7 +886,7 @@
         <v>1.4</v>
       </c>
       <c r="O5" t="n">
-        <v>148445737225</v>
+        <v>155007513245</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>기타법인의 자사주 매집과 2200억 규모의 수주 계약 공시 가능성 언급. 미국 증시 호조 및 급등 기대감 표출.</t>
+          <t>기타법인의 자사주 350만주 매집 소식과 미국 증시 호조 속 급등 기대감 형성. 2200억 규모 수주 계약 임박 및 Jp모건 순매수 확인.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['자사주 매집', '수주 계약', '급등 기대']</t>
+          <t>['자사주 매집', '수주 계약', 'Jp모건']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,79 +931,79 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>243500</v>
+        <v>10470</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.04%</t>
+          <t>'+8.27%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.04</v>
+        <v>0.17</v>
       </c>
       <c r="E6" t="n">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="F6" t="n">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="G6" t="n">
-        <v>610</v>
+        <v>245</v>
       </c>
       <c r="H6" t="n">
-        <v>4.12</v>
+        <v>5.01</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>241000</v>
+        <v>9670</v>
       </c>
       <c r="K6" t="n">
-        <v>253000</v>
+        <v>11020</v>
       </c>
       <c r="L6" t="n">
-        <v>257000</v>
+        <v>11030</v>
       </c>
       <c r="M6" t="n">
-        <v>235000</v>
+        <v>10300</v>
       </c>
       <c r="N6" t="n">
-        <v>4.08</v>
+        <v>4.84</v>
       </c>
       <c r="O6" t="n">
-        <v>64123040000</v>
+        <v>11795834040</v>
       </c>
       <c r="P6" t="n">
-        <v>1233000</v>
+        <v>15900</v>
       </c>
       <c r="Q6" t="n">
-        <v>120000</v>
+        <v>6310</v>
       </c>
       <c r="R6" t="n">
-        <v>-43000</v>
+        <v>-216000</v>
       </c>
       <c r="S6" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>경구용 인슐린 10조원대 L/O 예상 및 캐나다/독일 건 관련 긍정적 전망. 외국인 수급 개선 및 거래량 증가 추세 언급.</t>
+          <t>코로나19, 말라리아 등 다양한 질병 테마주로 언급되며 기대감 형성. 페스트, 에볼라 확산 관련 뉴스가 주가에 영향을 미칠 가능성 제기. 하지만 근거 희박한 테마주 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['경구용 인슐린', 'L/O 예상', '외국인 수급']</t>
+          <t>['테마주', '질병 확산', '기대감']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>274000</v>
+        <v>273000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.74%</t>
+          <t>'+0.37%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="G7" t="n">
-        <v>2355</v>
+        <v>2232</v>
       </c>
       <c r="H7" t="n">
         <v>46.37</v>
@@ -1070,7 +1070,7 @@
         <v>46.41</v>
       </c>
       <c r="O7" t="n">
-        <v>1583807903250</v>
+        <v>1702323609750</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>게시글에서 언급된 정치적, 사회적 이슈와는 무관하게 주가 및 투자 심리에 대한 구체적인 사실 기반 분석은 부재함.</t>
+          <t>자사주 매입 종료 후 주가 상승 기대에도 불구하고, 여러 정치적 논란과 기관/연기금의 매도세 언급으로 부정적 전망. 반도체 업황 부진 우려.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['자사주 매입', '반도체', '기관 매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>81600</v>
+        <v>81500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.03</v>
       </c>
       <c r="E8" t="n">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="F8" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G8" t="n">
-        <v>525</v>
+        <v>595</v>
       </c>
       <c r="H8" t="n">
         <v>22.59</v>
@@ -1162,7 +1162,7 @@
         <v>22.56</v>
       </c>
       <c r="O8" t="n">
-        <v>85543086050</v>
+        <v>89816998450</v>
       </c>
       <c r="P8" t="n">
         <v>139200</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 원전주 급등에 따른 기대감, 구글 계약 호재 언급.</t>
+          <t>구글의 미국 최대 원전기업과 전력구매 계약 체결 소식을 바탕으로 미국 원전주 급등에 따른 동반 상승 기대감 고조. 공매도 세력과의 전쟁 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['원전', '구글 계약']</t>
+          <t>['미국 원전', '전력구매 계약', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17630</v>
+        <v>17710</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.68%</t>
+          <t>'-0.23%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.11</v>
       </c>
       <c r="E9" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F9" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G9" t="n">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="H9" t="n">
         <v>9.5</v>
@@ -1254,7 +1254,7 @@
         <v>9.390000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>28099504315</v>
+        <v>29322338935</v>
       </c>
       <c r="P9" t="n">
         <v>40350</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>올해 수주 목표 언급 및 미국 원전 건설 분위기 긍정적 전망 제시. 다만, 주가 상승에 대한 기대와 달리 실제 움직임은 지연되며, 일부 부정적 의견도 혼재.</t>
+          <t>수주 목표 상향 및 미국 원전 건설 호재로 긍정적 전망. 싱가포르 수상 및 미국 원전 수주 가능성 언급. 반복되는 '호소'글은 투자자들의 간절함을 반영.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['수주 목표', '원전 건설', '주가 전망']</t>
+          <t>['수주 목표', '미국 원전', '안전 시공']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,83 +1299,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1756000</v>
+        <v>240000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.96%</t>
+          <t>'-0.41%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>128</v>
       </c>
       <c r="F10" t="n">
-        <v>459</v>
+        <v>88</v>
       </c>
       <c r="G10" t="n">
-        <v>2042</v>
+        <v>645</v>
       </c>
       <c r="H10" t="n">
-        <v>49.71</v>
+        <v>4.12</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1773000</v>
+        <v>241000</v>
       </c>
       <c r="K10" t="n">
-        <v>1728000</v>
+        <v>253000</v>
       </c>
       <c r="L10" t="n">
-        <v>1779000</v>
+        <v>257000</v>
       </c>
       <c r="M10" t="n">
-        <v>1725000</v>
+        <v>235000</v>
       </c>
       <c r="N10" t="n">
-        <v>49.76</v>
+        <v>4.08</v>
       </c>
       <c r="O10" t="n">
-        <v>1553763023500</v>
+        <v>65762895250</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>1233000</v>
       </c>
       <c r="Q10" t="n">
-        <v>403000</v>
+        <v>120000</v>
       </c>
       <c r="R10" t="n">
-        <v>-147000</v>
+        <v>-43000</v>
       </c>
       <c r="S10" t="n">
-        <v>-47000</v>
+        <v>2000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>SK하이닉스 ADR 급락 및 락업 해제 관련 부정적 뉴스 다수 언급. 실적 호조에도 불구하고 외국인 매도에 대한 의문 제기.</t>
+          <t>경구용 인슐린 10조원대 L/O 예상 및 캐나다, 독일 관련 기대감. 외국인 공매도 숏커버링 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['SK하이닉스 ADR', '락업 해제', '외국인 매도']</t>
+          <t>['경구용인슐린', 'L/O', '공매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18250</v>
+        <v>12900</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.51%</t>
+          <t>'-0.85%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.11</v>
+        <v>1.88</v>
       </c>
       <c r="E11" t="n">
-        <v>108</v>
+        <v>64</v>
       </c>
       <c r="F11" t="n">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="G11" t="n">
-        <v>651</v>
+        <v>137</v>
       </c>
       <c r="H11" t="n">
-        <v>4.92</v>
+        <v>1.42</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>18530</v>
+        <v>13010</v>
       </c>
       <c r="K11" t="n">
-        <v>18950</v>
+        <v>12330</v>
       </c>
       <c r="L11" t="n">
-        <v>19870</v>
+        <v>13560</v>
       </c>
       <c r="M11" t="n">
-        <v>18220</v>
+        <v>12260</v>
       </c>
       <c r="N11" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>221041941240</v>
+        <v>30990472000</v>
       </c>
       <c r="P11" t="n">
-        <v>31500</v>
+        <v>22250</v>
       </c>
       <c r="Q11" t="n">
-        <v>1272</v>
+        <v>6000</v>
       </c>
       <c r="R11" t="n">
-        <v>-317000</v>
+        <v>-100000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 광통신 주가 상승 및 젠슨 황의 광통신 지지 언급. 19,000원 안착 및 25,000원 돌파 기대감 나타남.</t>
+          <t>기타법인의 대량 자사주 매집과 유증 물량 출회 속에서 투자자들의 혼란과 경계심이 공존하고 있다. 일부는 호재 대기 및 매수 기회로 보고 있으나, 주가 조작 의혹 및 상장 물량 부담에 대한 우려도 제기된다.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', '미국 주가', '젠슨 황']</t>
+          <t>['자사주 매집', '유증 물량', '주가 조작']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46050</v>
+        <v>46900</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.85%</t>
+          <t>'-1.05%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="F12" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G12" t="n">
-        <v>1495</v>
+        <v>1532</v>
       </c>
       <c r="H12" t="n">
         <v>14.12</v>
@@ -1530,7 +1530,7 @@
         <v>14.1</v>
       </c>
       <c r="O12" t="n">
-        <v>26033353950</v>
+        <v>27138950550</v>
       </c>
       <c r="P12" t="n">
         <v>69200</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30550</v>
+        <v>1752000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.78%</t>
+          <t>'-1.18%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="E13" t="n">
-        <v>72</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>45</v>
+        <v>457</v>
       </c>
       <c r="G13" t="n">
-        <v>153</v>
+        <v>1996</v>
       </c>
       <c r="H13" t="n">
-        <v>10.78</v>
+        <v>49.71</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>31750</v>
+        <v>1773000</v>
       </c>
       <c r="K13" t="n">
-        <v>32600</v>
+        <v>1728000</v>
       </c>
       <c r="L13" t="n">
-        <v>32850</v>
+        <v>1779000</v>
       </c>
       <c r="M13" t="n">
-        <v>30500</v>
+        <v>1725000</v>
       </c>
       <c r="N13" t="n">
-        <v>10.77</v>
+        <v>49.76</v>
       </c>
       <c r="O13" t="n">
-        <v>62536949175</v>
+        <v>1634980119500</v>
       </c>
       <c r="P13" t="n">
-        <v>75900</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>15960</v>
+        <v>403000</v>
       </c>
       <c r="R13" t="n">
-        <v>-379000</v>
+        <v>-147000</v>
       </c>
       <c r="S13" t="n">
-        <v>-21000</v>
+        <v>-47000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>가온전선과의 비교를 통해 부진한 실적과 주가 흐름을 지적하며, 회사 내부 문제 및 주식 관리 부실에 대한 우려 제기. 일부 수주 건 언급 있으나 영향력 미미.</t>
+          <t>SK하이닉스 ADR 급락 소식에 따른 투자 심리 위축. 미장 폭락 선반영 및 락업 해제 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['가온전선', '주가 관리', '수주']</t>
+          <t>['ADR', '락업해제', '선반영']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12500</v>
+        <v>18230</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.92%</t>
+          <t>'-1.62%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.88</v>
+        <v>1.11</v>
       </c>
       <c r="E14" t="n">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="F14" t="n">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="G14" t="n">
-        <v>137</v>
+        <v>673</v>
       </c>
       <c r="H14" t="n">
-        <v>1.42</v>
+        <v>4.92</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,60 +1699,244 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>13010</v>
+        <v>18530</v>
       </c>
       <c r="K14" t="n">
-        <v>12330</v>
+        <v>18950</v>
       </c>
       <c r="L14" t="n">
-        <v>13560</v>
+        <v>19870</v>
       </c>
       <c r="M14" t="n">
-        <v>12260</v>
+        <v>18220</v>
       </c>
       <c r="N14" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="O14" t="n">
+        <v>225459554080</v>
+      </c>
+      <c r="P14" t="n">
+        <v>31500</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1272</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-317000</v>
+      </c>
+      <c r="S14" t="n">
         <v>0</v>
       </c>
-      <c r="O14" t="n">
-        <v>29744502725</v>
-      </c>
-      <c r="P14" t="n">
-        <v>22250</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>6000</v>
-      </c>
-      <c r="R14" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3000</v>
-      </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>기타법인의 대량 자사주 매집과 유증 물량 출회 속에서 투자자들의 혼란과 경계심이 공존하고 있다. 일부는 호재 대기 및 매수 기회로 보고 있으나, 주가 조작 의혹 및 상장 물량 부담에 대한 우려도 제기된다.</t>
+          <t>미국 광통신 주가 상승 및 젠슨 황의 광통신 지지 언급으로 신고가 달성 모멘텀 기대. 2만원 안착 및 25000원 돌파 가능성 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['자사주 매집', '유증 물량', '주가 조작']</t>
+          <t>['광통신', '신고가', '젠슨 황']</t>
         </is>
       </c>
       <c r="X14" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>아톤</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>6790</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>'-2.72%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="E15" t="n">
+        <v>44</v>
+      </c>
+      <c r="F15" t="n">
+        <v>35</v>
+      </c>
+      <c r="G15" t="n">
+        <v>121</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>6980</v>
+      </c>
+      <c r="K15" t="n">
+        <v>7000</v>
+      </c>
+      <c r="L15" t="n">
+        <v>7240</v>
+      </c>
+      <c r="M15" t="n">
+        <v>6580</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="O15" t="n">
+        <v>38915819780</v>
+      </c>
+      <c r="P15" t="n">
+        <v>11370</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3300</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-37000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>망분리 완화 정책에 따른 금융권 보안 시장 공략 및 3분기 역대급 실적 기대감. 라온시큐어와의 경쟁 구도 속 대장주 지위 경쟁.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>['망분리 완화', '금융권 보안', '실적 기대']</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
         <v>2</v>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>047920</t>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>158430</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>대한전선</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>30450</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>'-4.09%</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E16" t="n">
+        <v>75</v>
+      </c>
+      <c r="F16" t="n">
+        <v>47</v>
+      </c>
+      <c r="G16" t="n">
+        <v>158</v>
+      </c>
+      <c r="H16" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>31750</v>
+      </c>
+      <c r="K16" t="n">
+        <v>32600</v>
+      </c>
+      <c r="L16" t="n">
+        <v>32850</v>
+      </c>
+      <c r="M16" t="n">
+        <v>30400</v>
+      </c>
+      <c r="N16" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="O16" t="n">
+        <v>66001326175</v>
+      </c>
+      <c r="P16" t="n">
+        <v>75900</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>15960</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-379000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-21000</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>경쟁사 가온전선의 신고가 행진과 달리 큰 폭의 하락세를 보이며 주가 관리 부실 및 내부 문제 가능성 제기. 기관/외인 매도세 심화.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>['주가 관리', '기관 매도', '경쟁사 비교']</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>001440</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261007_10.xlsx
+++ b/data/trending_integrated_20261007_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,79 +563,79 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>제이앤티씨</t>
+          <t>국제약품</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26800</v>
+        <v>4430</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+16.78%</t>
+          <t>'+29.91%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.4</v>
+        <v>-0.08</v>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G2" t="n">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="H2" t="n">
-        <v>2.82</v>
+        <v>3.27</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>22950</v>
+        <v>3410</v>
       </c>
       <c r="K2" t="n">
-        <v>26200</v>
+        <v>3605</v>
       </c>
       <c r="L2" t="n">
-        <v>27600</v>
+        <v>4430</v>
       </c>
       <c r="M2" t="n">
-        <v>25550</v>
+        <v>3605</v>
       </c>
       <c r="N2" t="n">
-        <v>2.42</v>
+        <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>75345058500</v>
+        <v>25937005794</v>
       </c>
       <c r="P2" t="n">
-        <v>30100</v>
+        <v>5470</v>
       </c>
       <c r="Q2" t="n">
-        <v>11140</v>
+        <v>2810</v>
       </c>
       <c r="R2" t="n">
-        <v>158000</v>
+        <v>280000</v>
       </c>
       <c r="S2" t="n">
-        <v>-205000</v>
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>유증 관련 논쟁 속 유리 기술력에 대한 기대감 존재. 브로드컴, 인텔 돌파 가능성 언급.</t>
+          <t>국제약품, 흑사병 관련 테마주로 급등. 관련 뉴스 및 타사 동향 언급 있으나, 자체적인 팩트 기반 분석은 미흡.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['유증', '유리기술력', '주포']</t>
+          <t>['흑사병', '치료제', '테마주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>002720</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>제이앤티씨</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17130</v>
+        <v>26600</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.20%</t>
+          <t>'+15.90%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.98</v>
+        <v>0.4</v>
       </c>
       <c r="E3" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="F3" t="n">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="G3" t="n">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="H3" t="n">
-        <v>2.37</v>
+        <v>2.82</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>14870</v>
+        <v>22950</v>
       </c>
       <c r="K3" t="n">
-        <v>15480</v>
+        <v>26200</v>
       </c>
       <c r="L3" t="n">
-        <v>17590</v>
+        <v>27600</v>
       </c>
       <c r="M3" t="n">
-        <v>14600</v>
+        <v>25550</v>
       </c>
       <c r="N3" t="n">
-        <v>1.39</v>
+        <v>2.42</v>
       </c>
       <c r="O3" t="n">
-        <v>172966034555</v>
+        <v>77511722575</v>
       </c>
       <c r="P3" t="n">
-        <v>17590</v>
+        <v>30100</v>
       </c>
       <c r="Q3" t="n">
-        <v>6320</v>
+        <v>11140</v>
       </c>
       <c r="R3" t="n">
-        <v>-91000</v>
+        <v>158000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-205000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>개인정보 유출 및 해킹 사고 증가로 인한 보안 투자 확대 기대감. 농협, KDB생명 등 해킹 방어 이력 및 양자보안 공급 논의 언급. 보안 0티어 대장주로 신고가 돌파.</t>
+          <t>유리 기술력을 바탕으로 한 신규 사업 기대감 및 주포 세력의 움직임. 유상증자 이슈 속에서도 단기 급등 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['보안', '개인정보 유출', '양자보안']</t>
+          <t>['유리기판', '주포', '유상증자']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>204270</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7530</v>
+        <v>16920</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+11.56%</t>
+          <t>'+13.79%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.02</v>
+        <v>0.98</v>
       </c>
       <c r="E4" t="n">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="F4" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="G4" t="n">
-        <v>81</v>
+        <v>143</v>
       </c>
       <c r="H4" t="n">
-        <v>5.12</v>
+        <v>2.37</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>6750</v>
+        <v>14870</v>
       </c>
       <c r="K4" t="n">
-        <v>6710</v>
+        <v>15480</v>
       </c>
       <c r="L4" t="n">
-        <v>8310</v>
+        <v>17590</v>
       </c>
       <c r="M4" t="n">
-        <v>6690</v>
+        <v>14600</v>
       </c>
       <c r="N4" t="n">
-        <v>5.14</v>
+        <v>1.39</v>
       </c>
       <c r="O4" t="n">
-        <v>39614985300</v>
+        <v>184588081435</v>
       </c>
       <c r="P4" t="n">
-        <v>23500</v>
+        <v>17590</v>
       </c>
       <c r="Q4" t="n">
-        <v>2890</v>
+        <v>6320</v>
       </c>
       <c r="R4" t="n">
-        <v>-226000</v>
+        <v>-91000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정부의 용적률 상향 및 그린벨트 해제 기대감 속 건설 기초 소재 대장주로서 목표가 10만원 이상 제시. 외국인 프로그램 매수세 확인.</t>
+          <t>라온시큐어, 개인정보 유출 및 해킹 관련 뉴스와 연계되어 상승. 양자보안 공급 논의 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['건설 기초 소재', '용적률 상향', '외국인 매수']</t>
+          <t>['해킹', '보안', '양자보안']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5470</v>
+        <v>7540</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.18%</t>
+          <t>'+11.70%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.32</v>
+        <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="F5" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>155</v>
+        <v>95</v>
       </c>
       <c r="H5" t="n">
-        <v>4.72</v>
+        <v>5.12</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>5010</v>
+        <v>6750</v>
       </c>
       <c r="K5" t="n">
-        <v>5120</v>
+        <v>6710</v>
       </c>
       <c r="L5" t="n">
-        <v>5990</v>
+        <v>8310</v>
       </c>
       <c r="M5" t="n">
-        <v>4950</v>
+        <v>6690</v>
       </c>
       <c r="N5" t="n">
-        <v>1.4</v>
+        <v>5.14</v>
       </c>
       <c r="O5" t="n">
-        <v>155007513245</v>
+        <v>41808610370</v>
       </c>
       <c r="P5" t="n">
-        <v>8100</v>
+        <v>23500</v>
       </c>
       <c r="Q5" t="n">
-        <v>592</v>
+        <v>2890</v>
       </c>
       <c r="R5" t="n">
-        <v>1405000</v>
+        <v>-226000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>기타법인의 자사주 350만주 매집 소식과 미국 증시 호조 속 급등 기대감 형성. 2200억 규모 수주 계약 임박 및 Jp모건 순매수 확인.</t>
+          <t>정부의 용적률 상향 및 그린벨트 해제 정책으로 인한 건설 기초 소재 대장주로서의 기대감. 외국인 프로그램 매매세와 일시적 상승 흐름.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['자사주 매집', '수주 계약', 'Jp모건']</t>
+          <t>['용적률', '그린벨트', '건설기초소재']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10470</v>
+        <v>10660</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.27%</t>
+          <t>'+10.24%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.17</v>
       </c>
       <c r="E6" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F6" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G6" t="n">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="H6" t="n">
         <v>5.01</v>
@@ -978,7 +978,7 @@
         <v>4.84</v>
       </c>
       <c r="O6" t="n">
-        <v>11795834040</v>
+        <v>13544052570</v>
       </c>
       <c r="P6" t="n">
         <v>15900</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>코로나19, 말라리아 등 다양한 질병 테마주로 언급되며 기대감 형성. 페스트, 에볼라 확산 관련 뉴스가 주가에 영향을 미칠 가능성 제기. 하지만 근거 희박한 테마주 언급.</t>
+          <t>신풍제약, 다양한 질병 테마주로 언급되나, 흑사병 관련 뉴스와 연계된 기대감 위주.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['테마주', '질병 확산', '기대감']</t>
+          <t>['테마주', '흑사병', '백신']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,70 +1023,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>273000</v>
+        <v>2625</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.37%</t>
+          <t>'+10.06%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.04</v>
+        <v>-0.29</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>40</v>
       </c>
       <c r="F7" t="n">
-        <v>473</v>
+        <v>19</v>
       </c>
       <c r="G7" t="n">
-        <v>2232</v>
+        <v>55</v>
       </c>
       <c r="H7" t="n">
-        <v>46.37</v>
+        <v>0.82</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>272000</v>
+        <v>2385</v>
       </c>
       <c r="K7" t="n">
-        <v>269500</v>
+        <v>2510</v>
       </c>
       <c r="L7" t="n">
-        <v>279500</v>
+        <v>2900</v>
       </c>
       <c r="M7" t="n">
-        <v>268500</v>
+        <v>2505</v>
       </c>
       <c r="N7" t="n">
-        <v>46.41</v>
+        <v>1.11</v>
       </c>
       <c r="O7" t="n">
-        <v>1702323609750</v>
+        <v>8081827704</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>4760</v>
       </c>
       <c r="Q7" t="n">
-        <v>90200</v>
+        <v>973</v>
       </c>
       <c r="R7" t="n">
-        <v>1232000</v>
+        <v>-43000</v>
       </c>
       <c r="S7" t="n">
-        <v>-121000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>자사주 매입 종료 후 주가 상승 기대에도 불구하고, 여러 정치적 논란과 기관/연기금의 매도세 언급으로 부정적 전망. 반도체 업황 부진 우려.</t>
+          <t>바이오 섹터 내에서의 약세 및 개별 종목의 부진. 유상증자 관련 지분 매각 루머 및 단기적 수급 불안정성.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['자사주 매입', '반도체', '기관 매도']</t>
+          <t>['바이오', '수급', '유상증자']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,77 +1108,77 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>299660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>81500</v>
+        <v>5380</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+7.39%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.03</v>
+        <v>3.32</v>
       </c>
       <c r="E8" t="n">
-        <v>208</v>
+        <v>74</v>
       </c>
       <c r="F8" t="n">
-        <v>124</v>
+        <v>49</v>
       </c>
       <c r="G8" t="n">
-        <v>595</v>
+        <v>166</v>
       </c>
       <c r="H8" t="n">
-        <v>22.59</v>
+        <v>4.72</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>81500</v>
+        <v>5010</v>
       </c>
       <c r="K8" t="n">
-        <v>83500</v>
+        <v>5120</v>
       </c>
       <c r="L8" t="n">
-        <v>84300</v>
+        <v>5990</v>
       </c>
       <c r="M8" t="n">
-        <v>81500</v>
+        <v>4950</v>
       </c>
       <c r="N8" t="n">
-        <v>22.56</v>
+        <v>1.4</v>
       </c>
       <c r="O8" t="n">
-        <v>89816998450</v>
+        <v>161682961300</v>
       </c>
       <c r="P8" t="n">
-        <v>139200</v>
+        <v>8100</v>
       </c>
       <c r="Q8" t="n">
-        <v>57000</v>
+        <v>592</v>
       </c>
       <c r="R8" t="n">
-        <v>72000</v>
+        <v>1405000</v>
       </c>
       <c r="S8" t="n">
-        <v>-40000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>구글의 미국 최대 원전기업과 전력구매 계약 체결 소식을 바탕으로 미국 원전주 급등에 따른 동반 상승 기대감 고조. 공매도 세력과의 전쟁 언급.</t>
+          <t>빛과전자, 2200억 규모 수주 계약 기대감 및 기타법인 자사주 매집 언급. 공시 대기.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['미국 원전', '전력구매 계약', '공매도']</t>
+          <t>['수주', '자사주', '공시']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17710</v>
+        <v>274000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.23%</t>
+          <t>'+0.74%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.11</v>
+        <v>-0.04</v>
       </c>
       <c r="E9" t="n">
-        <v>44</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>28</v>
+        <v>478</v>
       </c>
       <c r="G9" t="n">
-        <v>209</v>
+        <v>1932</v>
       </c>
       <c r="H9" t="n">
-        <v>9.5</v>
+        <v>46.37</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,47 +1239,47 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>17750</v>
+        <v>272000</v>
       </c>
       <c r="K9" t="n">
-        <v>17970</v>
+        <v>269500</v>
       </c>
       <c r="L9" t="n">
-        <v>18030</v>
+        <v>279500</v>
       </c>
       <c r="M9" t="n">
-        <v>17610</v>
+        <v>268500</v>
       </c>
       <c r="N9" t="n">
-        <v>9.390000000000001</v>
+        <v>46.41</v>
       </c>
       <c r="O9" t="n">
-        <v>29322338935</v>
+        <v>1796723920750</v>
       </c>
       <c r="P9" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>3320</v>
+        <v>90200</v>
       </c>
       <c r="R9" t="n">
-        <v>-95000</v>
+        <v>1232000</v>
       </c>
       <c r="S9" t="n">
-        <v>-29000</v>
+        <v>-121000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>수주 목표 상향 및 미국 원전 건설 호재로 긍정적 전망. 싱가포르 수상 및 미국 원전 수주 가능성 언급. 반복되는 '호소'글은 투자자들의 간절함을 반영.</t>
+          <t>삼성전자, 정치적 이슈와 증시 비판 관련 게시글 다수. 실제 투자 근거는 부족.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['수주 목표', '미국 원전', '안전 시공']</t>
+          <t>['기관', '연기금', '증시']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,86 +1292,86 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>240000</v>
+        <v>81700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.41%</t>
+          <t>'+0.25%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E10" t="n">
-        <v>128</v>
+        <v>220</v>
       </c>
       <c r="F10" t="n">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="G10" t="n">
-        <v>645</v>
+        <v>612</v>
       </c>
       <c r="H10" t="n">
-        <v>4.12</v>
+        <v>22.59</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>241000</v>
+        <v>81500</v>
       </c>
       <c r="K10" t="n">
-        <v>253000</v>
+        <v>83500</v>
       </c>
       <c r="L10" t="n">
-        <v>257000</v>
+        <v>84300</v>
       </c>
       <c r="M10" t="n">
-        <v>235000</v>
+        <v>81500</v>
       </c>
       <c r="N10" t="n">
-        <v>4.08</v>
+        <v>22.56</v>
       </c>
       <c r="O10" t="n">
-        <v>65762895250</v>
+        <v>92663260050</v>
       </c>
       <c r="P10" t="n">
-        <v>1233000</v>
+        <v>139200</v>
       </c>
       <c r="Q10" t="n">
-        <v>120000</v>
+        <v>57000</v>
       </c>
       <c r="R10" t="n">
-        <v>-43000</v>
+        <v>72000</v>
       </c>
       <c r="S10" t="n">
-        <v>2000</v>
+        <v>-40000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>경구용 인슐린 10조원대 L/O 예상 및 캐나다, 독일 관련 기대감. 외국인 공매도 숏커버링 언급.</t>
+          <t>구글의 미국 최대 원전기업과 전력구매 계약 체결 소식을 바탕으로 미국 원전주 급등에 따른 동반 상승 기대감 고조. 공매도 세력과의 전쟁 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['경구용인슐린', 'L/O', '공매도']</t>
+          <t>['미국 원전', '전력구매 계약', '공매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12900</v>
+        <v>240000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.85%</t>
+          <t>'-0.41%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.88</v>
+        <v>0.04</v>
       </c>
       <c r="E11" t="n">
-        <v>64</v>
+        <v>131</v>
       </c>
       <c r="F11" t="n">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="G11" t="n">
-        <v>137</v>
+        <v>669</v>
       </c>
       <c r="H11" t="n">
-        <v>1.42</v>
+        <v>4.12</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>13010</v>
+        <v>241000</v>
       </c>
       <c r="K11" t="n">
-        <v>12330</v>
+        <v>253000</v>
       </c>
       <c r="L11" t="n">
-        <v>13560</v>
+        <v>257000</v>
       </c>
       <c r="M11" t="n">
-        <v>12260</v>
+        <v>235000</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="O11" t="n">
-        <v>30990472000</v>
+        <v>66755061500</v>
       </c>
       <c r="P11" t="n">
-        <v>22250</v>
+        <v>1233000</v>
       </c>
       <c r="Q11" t="n">
-        <v>6000</v>
+        <v>120000</v>
       </c>
       <c r="R11" t="n">
-        <v>-100000</v>
+        <v>-43000</v>
       </c>
       <c r="S11" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>기타법인의 대량 자사주 매집과 유증 물량 출회 속에서 투자자들의 혼란과 경계심이 공존하고 있다. 일부는 호재 대기 및 매수 기회로 보고 있으나, 주가 조작 의혹 및 상장 물량 부담에 대한 우려도 제기된다.</t>
+          <t>경구용 인슐린 10조원대 L/O 예상 및 캐나다, 독일 관련 기대감. 외국인 공매도 숏커버링 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['자사주 매집', '유증 물량', '주가 조작']</t>
+          <t>['경구용인슐린', 'L/O', '공매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,77 +1476,77 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46900</v>
+        <v>17650</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.05%</t>
+          <t>'-0.56%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.02</v>
+        <v>0.11</v>
       </c>
       <c r="E12" t="n">
-        <v>235</v>
+        <v>44</v>
       </c>
       <c r="F12" t="n">
-        <v>149</v>
+        <v>29</v>
       </c>
       <c r="G12" t="n">
-        <v>1532</v>
+        <v>227</v>
       </c>
       <c r="H12" t="n">
-        <v>14.12</v>
+        <v>9.5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>47400</v>
+        <v>17750</v>
       </c>
       <c r="K12" t="n">
-        <v>46350</v>
+        <v>17970</v>
       </c>
       <c r="L12" t="n">
-        <v>47850</v>
+        <v>18030</v>
       </c>
       <c r="M12" t="n">
-        <v>45650</v>
+        <v>17610</v>
       </c>
       <c r="N12" t="n">
-        <v>14.1</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>27138950550</v>
+        <v>30125928880</v>
       </c>
       <c r="P12" t="n">
-        <v>69200</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>24150</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>5000</v>
+        <v>-95000</v>
       </c>
       <c r="S12" t="n">
-        <v>2000</v>
+        <v>-29000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>FDA 승인 가능성 90% 이상 언급 및 시총 100조원 목표 제시. 공매도 세력에 대한 비판과 함께 대세 우상향 전망.</t>
+          <t>대우건설, 수주 목표 및 미국 원전 건설 분위기 긍정적 언급. 주주 호소 글 다수, 객관적 분석은 부족.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['FDA 승인', '공매도', '대세 우상향']</t>
+          <t>['수주', '원전', '주주']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1752000</v>
+        <v>13260</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.18%</t>
+          <t>'-0.97%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>41</v>
       </c>
       <c r="F13" t="n">
-        <v>457</v>
+        <v>23</v>
       </c>
       <c r="G13" t="n">
-        <v>1996</v>
+        <v>68</v>
       </c>
       <c r="H13" t="n">
-        <v>49.71</v>
+        <v>3.18</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1773000</v>
+        <v>13390</v>
       </c>
       <c r="K13" t="n">
-        <v>1728000</v>
+        <v>13770</v>
       </c>
       <c r="L13" t="n">
-        <v>1779000</v>
+        <v>13830</v>
       </c>
       <c r="M13" t="n">
-        <v>1725000</v>
+        <v>13210</v>
       </c>
       <c r="N13" t="n">
-        <v>49.76</v>
+        <v>3.12</v>
       </c>
       <c r="O13" t="n">
-        <v>1634980119500</v>
+        <v>21888653325</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>20300</v>
       </c>
       <c r="Q13" t="n">
-        <v>403000</v>
+        <v>3020</v>
       </c>
       <c r="R13" t="n">
-        <v>-147000</v>
+        <v>-255000</v>
       </c>
       <c r="S13" t="n">
-        <v>-47000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>SK하이닉스 ADR 급락 소식에 따른 투자 심리 위축. 미장 폭락 선반영 및 락업 해제 우려.</t>
+          <t>대원전선, 전선주 전반에 대한 언급과 기대감 있으나, 자체적인 팩트나 명확한 근거 부족.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['ADR', '락업해제', '선반영']</t>
+          <t>['전선주', '구리', '공시']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,86 +1660,86 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18230</v>
+        <v>1751000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.62%</t>
+          <t>'-1.24%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.11</v>
+        <v>-0.05</v>
       </c>
       <c r="E14" t="n">
-        <v>114</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>85</v>
+        <v>454</v>
       </c>
       <c r="G14" t="n">
-        <v>673</v>
+        <v>1916</v>
       </c>
       <c r="H14" t="n">
-        <v>4.92</v>
+        <v>49.71</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>18530</v>
+        <v>1773000</v>
       </c>
       <c r="K14" t="n">
-        <v>18950</v>
+        <v>1728000</v>
       </c>
       <c r="L14" t="n">
-        <v>19870</v>
+        <v>1779000</v>
       </c>
       <c r="M14" t="n">
-        <v>18220</v>
+        <v>1725000</v>
       </c>
       <c r="N14" t="n">
-        <v>3.81</v>
+        <v>49.76</v>
       </c>
       <c r="O14" t="n">
-        <v>225459554080</v>
+        <v>1728239628000</v>
       </c>
       <c r="P14" t="n">
-        <v>31500</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>1272</v>
+        <v>403000</v>
       </c>
       <c r="R14" t="n">
-        <v>-317000</v>
+        <v>-147000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-47000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 광통신 주가 상승 및 젠슨 황의 광통신 지지 언급으로 신고가 달성 모멘텀 기대. 2만원 안착 및 25000원 돌파 가능성 언급.</t>
+          <t>미국 ADR 급락 및 유럽 증시 하락 영향. 개인 투자자들의 우려와 자사주 매입 관련 전략에 대한 해석. 단기적 하락 추세.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['광통신', '신고가', '젠슨 황']</t>
+          <t>['ADR', '급락', '자사주']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6790</v>
+        <v>18290</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.72%</t>
+          <t>'-1.30%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.77</v>
+        <v>1.11</v>
       </c>
       <c r="E15" t="n">
-        <v>44</v>
+        <v>123</v>
       </c>
       <c r="F15" t="n">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="G15" t="n">
-        <v>121</v>
+        <v>729</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1</v>
+        <v>4.92</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>6980</v>
+        <v>18530</v>
       </c>
       <c r="K15" t="n">
-        <v>7000</v>
+        <v>18950</v>
       </c>
       <c r="L15" t="n">
-        <v>7240</v>
+        <v>19870</v>
       </c>
       <c r="M15" t="n">
-        <v>6580</v>
+        <v>18220</v>
       </c>
       <c r="N15" t="n">
-        <v>1.87</v>
+        <v>3.81</v>
       </c>
       <c r="O15" t="n">
-        <v>38915819780</v>
+        <v>228993500585</v>
       </c>
       <c r="P15" t="n">
-        <v>11370</v>
+        <v>31500</v>
       </c>
       <c r="Q15" t="n">
-        <v>3300</v>
+        <v>1272</v>
       </c>
       <c r="R15" t="n">
-        <v>-37000</v>
+        <v>-317000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>망분리 완화 정책에 따른 금융권 보안 시장 공략 및 3분기 역대급 실적 기대감. 라온시큐어와의 경쟁 구도 속 대장주 지위 경쟁.</t>
+          <t>대한광통신, 미국 광통신 주가 동향 및 젠슨 황의 광통신 지지 언급. 신고가 기대감.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['망분리 완화', '금융권 보안', '실적 기대']</t>
+          <t>['광통신', '미국', '신고가']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,97 +1844,373 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>30450</v>
+        <v>12810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.09%</t>
+          <t>'-1.54%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.01</v>
+        <v>1.88</v>
       </c>
       <c r="E16" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F16" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G16" t="n">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="H16" t="n">
-        <v>10.78</v>
+        <v>1.42</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>31750</v>
+        <v>13010</v>
       </c>
       <c r="K16" t="n">
-        <v>32600</v>
+        <v>12330</v>
       </c>
       <c r="L16" t="n">
-        <v>32850</v>
+        <v>13560</v>
       </c>
       <c r="M16" t="n">
-        <v>30400</v>
+        <v>12260</v>
       </c>
       <c r="N16" t="n">
-        <v>10.77</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>66001326175</v>
+        <v>32136208105</v>
       </c>
       <c r="P16" t="n">
-        <v>75900</v>
+        <v>22250</v>
       </c>
       <c r="Q16" t="n">
-        <v>15960</v>
+        <v>6000</v>
       </c>
       <c r="R16" t="n">
-        <v>-379000</v>
+        <v>-100000</v>
       </c>
       <c r="S16" t="n">
-        <v>-21000</v>
+        <v>3000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>경쟁사 가온전선의 신고가 행진과 달리 큰 폭의 하락세를 보이며 주가 관리 부실 및 내부 문제 가능성 제기. 기관/외인 매도세 심화.</t>
+          <t>기타 법인의 자사주 매집과 신규 상장 물량 부담 속에서의 주가 움직임. 유증 물량 소화 과정 및 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['주가 관리', '기관 매도', '경쟁사 비교']</t>
+          <t>['자사주', '유상증자', '주가조작']</t>
         </is>
       </c>
       <c r="X16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>047920</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>HLB</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>46600</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>'-1.69%</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E17" t="n">
+        <v>244</v>
+      </c>
+      <c r="F17" t="n">
+        <v>152</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1576</v>
+      </c>
+      <c r="H17" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>47400</v>
+      </c>
+      <c r="K17" t="n">
+        <v>46350</v>
+      </c>
+      <c r="L17" t="n">
+        <v>47850</v>
+      </c>
+      <c r="M17" t="n">
+        <v>45650</v>
+      </c>
+      <c r="N17" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>28145221675</v>
+      </c>
+      <c r="P17" t="n">
+        <v>69200</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>24150</v>
+      </c>
+      <c r="R17" t="n">
+        <v>5000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>FDA 승인 가능성 90% 이상 언급 및 시총 100조원 목표 제시. 공매도 세력에 대한 비판과 함께 대세 우상향 전망.</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>['FDA 승인', '공매도', '대세 우상향']</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>028300</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>아톤</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>6740</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>'-3.44%</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="E18" t="n">
+        <v>49</v>
+      </c>
+      <c r="F18" t="n">
+        <v>36</v>
+      </c>
+      <c r="G18" t="n">
+        <v>140</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>6980</v>
+      </c>
+      <c r="K18" t="n">
+        <v>7000</v>
+      </c>
+      <c r="L18" t="n">
+        <v>7240</v>
+      </c>
+      <c r="M18" t="n">
+        <v>6580</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="O18" t="n">
+        <v>39686889600</v>
+      </c>
+      <c r="P18" t="n">
+        <v>11370</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3300</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-37000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>아톤, 망분리 완화 및 금융권 공략 관련 언급. 라온시큐어와 비교되며 기대감 형성.</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>['보안', '망분리', '금융권']</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>158430</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>대한전선</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>30450</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>'-4.09%</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E19" t="n">
+        <v>85</v>
+      </c>
+      <c r="F19" t="n">
+        <v>53</v>
+      </c>
+      <c r="G19" t="n">
+        <v>177</v>
+      </c>
+      <c r="H19" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>31750</v>
+      </c>
+      <c r="K19" t="n">
+        <v>32600</v>
+      </c>
+      <c r="L19" t="n">
+        <v>32850</v>
+      </c>
+      <c r="M19" t="n">
+        <v>30300</v>
+      </c>
+      <c r="N19" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="O19" t="n">
+        <v>68700702275</v>
+      </c>
+      <c r="P19" t="n">
+        <v>75900</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>15960</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-379000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-21000</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>대한전선, 경쟁사(가온전선)와 비교되며 부진한 실적 및 주가 관리 문제 지적. 외인 매도세 언급.</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>['가온전선', '실적', '외인']</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
         <v>1</v>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>001440</t>
         </is>

--- a/data/trending_integrated_20261007_10.xlsx
+++ b/data/trending_integrated_20261007_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z19"/>
+  <dimension ref="A1:Z20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-0.08</v>
       </c>
       <c r="E2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F2" t="n">
         <v>31</v>
       </c>
       <c r="G2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H2" t="n">
         <v>3.27</v>
@@ -610,7 +610,7 @@
         <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>25937005794</v>
+        <v>26002645104</v>
       </c>
       <c r="P2" t="n">
         <v>5470</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>국제약품, 흑사병 관련 테마주로 급등. 관련 뉴스 및 타사 동향 언급 있으나, 자체적인 팩트 기반 분석은 미흡.</t>
+          <t>흑사병 테마 치료제 관련 기대감 상승. FDA 언급 및 다수 관련주 동반 강세.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['흑사병', '치료제', '테마주']</t>
+          <t>['흑사병', '치료제', 'FDA']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26600</v>
+        <v>26550</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.90%</t>
+          <t>'+15.69%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -676,7 +676,7 @@
         <v>31</v>
       </c>
       <c r="G3" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="H3" t="n">
         <v>2.82</v>
@@ -702,7 +702,7 @@
         <v>2.42</v>
       </c>
       <c r="O3" t="n">
-        <v>77511722575</v>
+        <v>78489888175</v>
       </c>
       <c r="P3" t="n">
         <v>30100</v>
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16920</v>
+        <v>7710</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.79%</t>
+          <t>'+14.22%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.98</v>
+        <v>-0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="F4" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="G4" t="n">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="H4" t="n">
-        <v>2.37</v>
+        <v>5.12</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>14870</v>
+        <v>6750</v>
       </c>
       <c r="K4" t="n">
-        <v>15480</v>
+        <v>6710</v>
       </c>
       <c r="L4" t="n">
-        <v>17590</v>
+        <v>8310</v>
       </c>
       <c r="M4" t="n">
-        <v>14600</v>
+        <v>6690</v>
       </c>
       <c r="N4" t="n">
-        <v>1.39</v>
+        <v>5.14</v>
       </c>
       <c r="O4" t="n">
-        <v>184588081435</v>
+        <v>44792138445</v>
       </c>
       <c r="P4" t="n">
-        <v>17590</v>
+        <v>23500</v>
       </c>
       <c r="Q4" t="n">
-        <v>6320</v>
+        <v>2890</v>
       </c>
       <c r="R4" t="n">
-        <v>-91000</v>
+        <v>-226000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>라온시큐어, 개인정보 유출 및 해킹 관련 뉴스와 연계되어 상승. 양자보안 공급 논의 언급.</t>
+          <t>정부의 용적률 상향 및 그린벨트 해제 검토 발표에 따른 건설 기대감. 대형 프로젝트 참여 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['해킹', '보안', '양자보안']</t>
+          <t>['용적률', '그린벨트', '건설']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7540</v>
+        <v>16900</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.70%</t>
+          <t>'+13.65%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.02</v>
+        <v>0.98</v>
       </c>
       <c r="E5" t="n">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="G5" t="n">
-        <v>95</v>
+        <v>151</v>
       </c>
       <c r="H5" t="n">
-        <v>5.12</v>
+        <v>2.37</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>6750</v>
+        <v>14870</v>
       </c>
       <c r="K5" t="n">
-        <v>6710</v>
+        <v>15480</v>
       </c>
       <c r="L5" t="n">
-        <v>8310</v>
+        <v>17590</v>
       </c>
       <c r="M5" t="n">
-        <v>6690</v>
+        <v>14600</v>
       </c>
       <c r="N5" t="n">
-        <v>5.14</v>
+        <v>1.39</v>
       </c>
       <c r="O5" t="n">
-        <v>41808610370</v>
+        <v>190350336615</v>
       </c>
       <c r="P5" t="n">
-        <v>23500</v>
+        <v>17590</v>
       </c>
       <c r="Q5" t="n">
-        <v>2890</v>
+        <v>6320</v>
       </c>
       <c r="R5" t="n">
-        <v>-226000</v>
+        <v>-91000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정부의 용적률 상향 및 그린벨트 해제 정책으로 인한 건설 기초 소재 대장주로서의 기대감. 외국인 프로그램 매매세와 일시적 상승 흐름.</t>
+          <t>개인정보 유출 및 해킹 관련 이슈 부각으로 인한 보안주 강세. 라온의 양자보안 기술력 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['용적률', '그린벨트', '건설기초소재']</t>
+          <t>['개인정보 유출', '보안주', '양자보안']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,86 +924,86 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10660</v>
+        <v>13740</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.24%</t>
+          <t>'+11.44%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="E6" t="n">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="G6" t="n">
-        <v>264</v>
+        <v>55</v>
       </c>
       <c r="H6" t="n">
-        <v>5.01</v>
+        <v>0.79</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>9670</v>
+        <v>12330</v>
       </c>
       <c r="K6" t="n">
-        <v>11020</v>
+        <v>12580</v>
       </c>
       <c r="L6" t="n">
-        <v>11030</v>
+        <v>13830</v>
       </c>
       <c r="M6" t="n">
-        <v>10300</v>
+        <v>12300</v>
       </c>
       <c r="N6" t="n">
-        <v>4.84</v>
+        <v>0.48</v>
       </c>
       <c r="O6" t="n">
-        <v>13544052570</v>
+        <v>96751679010</v>
       </c>
       <c r="P6" t="n">
-        <v>15900</v>
+        <v>20850</v>
       </c>
       <c r="Q6" t="n">
-        <v>6310</v>
+        <v>4020</v>
       </c>
       <c r="R6" t="n">
-        <v>-216000</v>
+        <v>-5000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>신풍제약, 다양한 질병 테마주로 언급되나, 흑사병 관련 뉴스와 연계된 기대감 위주.</t>
+          <t>미국 가스발전향 가스터빈 블레이드 독점 공급 계약 뉴스. 한화파워 납품 개시 사실 기반 긍정적 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['테마주', '흑사병', '백신']</t>
+          <t>['가스터빈', '블레이드', '독점 공급']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,86 +1016,86 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2625</v>
+        <v>10650</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+10.06%</t>
+          <t>'+10.13%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.29</v>
+        <v>0.17</v>
       </c>
       <c r="E7" t="n">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="F7" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="G7" t="n">
-        <v>55</v>
+        <v>266</v>
       </c>
       <c r="H7" t="n">
-        <v>0.82</v>
+        <v>5.01</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2385</v>
+        <v>9670</v>
       </c>
       <c r="K7" t="n">
-        <v>2510</v>
+        <v>11020</v>
       </c>
       <c r="L7" t="n">
-        <v>2900</v>
+        <v>11030</v>
       </c>
       <c r="M7" t="n">
-        <v>2505</v>
+        <v>10300</v>
       </c>
       <c r="N7" t="n">
-        <v>1.11</v>
+        <v>4.84</v>
       </c>
       <c r="O7" t="n">
-        <v>8081827704</v>
+        <v>14175465905</v>
       </c>
       <c r="P7" t="n">
-        <v>4760</v>
+        <v>15900</v>
       </c>
       <c r="Q7" t="n">
-        <v>973</v>
+        <v>6310</v>
       </c>
       <c r="R7" t="n">
-        <v>-43000</v>
+        <v>-216000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>바이오 섹터 내에서의 약세 및 개별 종목의 부진. 유상증자 관련 지분 매각 루머 및 단기적 수급 불안정성.</t>
+          <t>신풍제약, 다양한 질병 테마주로 언급되나, 흑사병 관련 뉴스와 연계된 기대감 위주.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['바이오', '수급', '유상증자']</t>
+          <t>['테마주', '흑사병', '백신']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>299660</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5380</v>
+        <v>2625</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+7.39%</t>
+          <t>'+10.06%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3.32</v>
+        <v>-0.29</v>
       </c>
       <c r="E8" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="F8" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="G8" t="n">
-        <v>166</v>
+        <v>57</v>
       </c>
       <c r="H8" t="n">
-        <v>4.72</v>
+        <v>0.82</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>5010</v>
+        <v>2385</v>
       </c>
       <c r="K8" t="n">
-        <v>5120</v>
+        <v>2510</v>
       </c>
       <c r="L8" t="n">
-        <v>5990</v>
+        <v>2900</v>
       </c>
       <c r="M8" t="n">
-        <v>4950</v>
+        <v>2505</v>
       </c>
       <c r="N8" t="n">
-        <v>1.4</v>
+        <v>1.11</v>
       </c>
       <c r="O8" t="n">
-        <v>161682961300</v>
+        <v>8144983854</v>
       </c>
       <c r="P8" t="n">
-        <v>8100</v>
+        <v>4760</v>
       </c>
       <c r="Q8" t="n">
-        <v>592</v>
+        <v>973</v>
       </c>
       <c r="R8" t="n">
-        <v>1405000</v>
+        <v>-43000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>빛과전자, 2200억 규모 수주 계약 기대감 및 기타법인 자사주 매집 언급. 공시 대기.</t>
+          <t>바이오 섹터 전반의 부진 속에서의 기술적 반등 시도. 유상증자 관련 지분 매각 이슈.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['수주', '자사주', '공시']</t>
+          <t>['바이오', '유상증자', '기술적 반등']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>299660</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>274000</v>
+        <v>5290</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.74%</t>
+          <t>'+5.59%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.04</v>
+        <v>3.32</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>80</v>
       </c>
       <c r="F9" t="n">
-        <v>478</v>
+        <v>52</v>
       </c>
       <c r="G9" t="n">
-        <v>1932</v>
+        <v>176</v>
       </c>
       <c r="H9" t="n">
-        <v>46.37</v>
+        <v>4.72</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>272000</v>
+        <v>5010</v>
       </c>
       <c r="K9" t="n">
-        <v>269500</v>
+        <v>5120</v>
       </c>
       <c r="L9" t="n">
-        <v>279500</v>
+        <v>5990</v>
       </c>
       <c r="M9" t="n">
-        <v>268500</v>
+        <v>4950</v>
       </c>
       <c r="N9" t="n">
-        <v>46.41</v>
+        <v>1.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1796723920750</v>
+        <v>167118025095</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>8100</v>
       </c>
       <c r="Q9" t="n">
-        <v>90200</v>
+        <v>592</v>
       </c>
       <c r="R9" t="n">
-        <v>1232000</v>
+        <v>1405000</v>
       </c>
       <c r="S9" t="n">
-        <v>-121000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>삼성전자, 정치적 이슈와 증시 비판 관련 게시글 다수. 실제 투자 근거는 부족.</t>
+          <t>기타법인의 자사주 매집 및 2200억 규모 수주 계약 기대감. 미국 시장 호조에 따른 긍정적 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['기관', '연기금', '증시']</t>
+          <t>['자사주 매집', '수주 계약', '미국 시장']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>81700</v>
+        <v>272750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.25%</t>
+          <t>'+0.28%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>220</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>132</v>
+        <v>466</v>
       </c>
       <c r="G10" t="n">
-        <v>612</v>
+        <v>1860</v>
       </c>
       <c r="H10" t="n">
-        <v>22.59</v>
+        <v>46.37</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>81500</v>
+        <v>272000</v>
       </c>
       <c r="K10" t="n">
-        <v>83500</v>
+        <v>269500</v>
       </c>
       <c r="L10" t="n">
-        <v>84300</v>
+        <v>279500</v>
       </c>
       <c r="M10" t="n">
-        <v>81500</v>
+        <v>268500</v>
       </c>
       <c r="N10" t="n">
-        <v>22.56</v>
+        <v>46.41</v>
       </c>
       <c r="O10" t="n">
-        <v>92663260050</v>
+        <v>1882029395500</v>
       </c>
       <c r="P10" t="n">
-        <v>139200</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>57000</v>
+        <v>90200</v>
       </c>
       <c r="R10" t="n">
-        <v>72000</v>
+        <v>1232000</v>
       </c>
       <c r="S10" t="n">
-        <v>-40000</v>
+        <v>-121000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>구글의 미국 최대 원전기업과 전력구매 계약 체결 소식을 바탕으로 미국 원전주 급등에 따른 동반 상승 기대감 고조. 공매도 세력과의 전쟁 언급.</t>
+          <t>총 영업이익 대비 낮은 주가에 대한 불만 표출. 정치적 이슈와 기관/연기금 매도에 대한 부정적 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['미국 원전', '전력구매 계약', '공매도']</t>
+          <t>['영업이익', '주가', '기관']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,86 +1384,86 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>240000</v>
+        <v>81600</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.41%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E11" t="n">
-        <v>131</v>
+        <v>227</v>
       </c>
       <c r="F11" t="n">
-        <v>90</v>
+        <v>134</v>
       </c>
       <c r="G11" t="n">
-        <v>669</v>
+        <v>627</v>
       </c>
       <c r="H11" t="n">
-        <v>4.12</v>
+        <v>22.59</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>241000</v>
+        <v>81500</v>
       </c>
       <c r="K11" t="n">
-        <v>253000</v>
+        <v>83500</v>
       </c>
       <c r="L11" t="n">
-        <v>257000</v>
+        <v>84300</v>
       </c>
       <c r="M11" t="n">
-        <v>235000</v>
+        <v>81500</v>
       </c>
       <c r="N11" t="n">
-        <v>4.08</v>
+        <v>22.56</v>
       </c>
       <c r="O11" t="n">
-        <v>66755061500</v>
+        <v>96519610800</v>
       </c>
       <c r="P11" t="n">
-        <v>1233000</v>
+        <v>139200</v>
       </c>
       <c r="Q11" t="n">
-        <v>120000</v>
+        <v>57000</v>
       </c>
       <c r="R11" t="n">
-        <v>-43000</v>
+        <v>72000</v>
       </c>
       <c r="S11" t="n">
-        <v>2000</v>
+        <v>-40000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>경구용 인슐린 10조원대 L/O 예상 및 캐나다, 독일 관련 기대감. 외국인 공매도 숏커버링 언급.</t>
+          <t>구글의 미국 최대 원전기업과 전력구매 계약 체결 소식을 바탕으로 미국 원전주 급등에 따른 동반 상승 기대감 고조. 공매도 세력과의 전쟁 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['경구용인슐린', 'L/O', '공매도']</t>
+          <t>['미국 원전', '전력구매 계약', '공매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17650</v>
+        <v>17640</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.56%</t>
+          <t>'-0.62%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.11</v>
       </c>
       <c r="E12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G12" t="n">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H12" t="n">
         <v>9.5</v>
@@ -1530,7 +1530,7 @@
         <v>9.390000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>30125928880</v>
+        <v>31459961060</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13260</v>
+        <v>13250</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.97%</t>
+          <t>'-1.05%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G13" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H13" t="n">
         <v>3.18</v>
@@ -1622,7 +1622,7 @@
         <v>3.12</v>
       </c>
       <c r="O13" t="n">
-        <v>21888653325</v>
+        <v>22065703535</v>
       </c>
       <c r="P13" t="n">
         <v>20300</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>대원전선, 전선주 전반에 대한 언급과 기대감 있으나, 자체적인 팩트나 명확한 근거 부족.</t>
+          <t>최근 주가 하락 및 박스권 흐름에 대한 답답함 표출. 공매도 및 외국인 매도에 대한 의심.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['전선주', '구리', '공시']</t>
+          <t>['전선주', '박스권', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,11 +1667,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1751000</v>
+        <v>238000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1679,71 +1679,71 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>134</v>
       </c>
       <c r="F14" t="n">
-        <v>454</v>
+        <v>91</v>
       </c>
       <c r="G14" t="n">
-        <v>1916</v>
+        <v>691</v>
       </c>
       <c r="H14" t="n">
-        <v>49.71</v>
+        <v>4.12</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1773000</v>
+        <v>241000</v>
       </c>
       <c r="K14" t="n">
-        <v>1728000</v>
+        <v>253000</v>
       </c>
       <c r="L14" t="n">
-        <v>1779000</v>
+        <v>257000</v>
       </c>
       <c r="M14" t="n">
-        <v>1725000</v>
+        <v>235000</v>
       </c>
       <c r="N14" t="n">
-        <v>49.76</v>
+        <v>4.08</v>
       </c>
       <c r="O14" t="n">
-        <v>1728239628000</v>
+        <v>68194232000</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>1233000</v>
       </c>
       <c r="Q14" t="n">
-        <v>403000</v>
+        <v>120000</v>
       </c>
       <c r="R14" t="n">
-        <v>-147000</v>
+        <v>-43000</v>
       </c>
       <c r="S14" t="n">
-        <v>-47000</v>
+        <v>2000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 ADR 급락 및 유럽 증시 하락 영향. 개인 투자자들의 우려와 자사주 매입 관련 전략에 대한 해석. 단기적 하락 추세.</t>
+          <t>경구용 인슐린 10조원대 LO 예상 및 캐나다/독일 관련 뉴스 기대감 형성. 외국인 숏커버링 추정 수급 동향 관찰.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['ADR', '급락', '자사주']</t>
+          <t>['경구용 인슐린', '공매도', '숏커버링']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,86 +1752,86 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18290</v>
+        <v>1745000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.30%</t>
+          <t>'-1.58%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.11</v>
+        <v>-0.05</v>
       </c>
       <c r="E15" t="n">
-        <v>123</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>89</v>
+        <v>456</v>
       </c>
       <c r="G15" t="n">
-        <v>729</v>
+        <v>1745</v>
       </c>
       <c r="H15" t="n">
-        <v>4.92</v>
+        <v>49.71</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>18530</v>
+        <v>1773000</v>
       </c>
       <c r="K15" t="n">
-        <v>18950</v>
+        <v>1728000</v>
       </c>
       <c r="L15" t="n">
-        <v>19870</v>
+        <v>1779000</v>
       </c>
       <c r="M15" t="n">
-        <v>18220</v>
+        <v>1725000</v>
       </c>
       <c r="N15" t="n">
-        <v>3.81</v>
+        <v>49.76</v>
       </c>
       <c r="O15" t="n">
-        <v>228993500585</v>
+        <v>1823028353500</v>
       </c>
       <c r="P15" t="n">
-        <v>31500</v>
+        <v>2987000</v>
       </c>
       <c r="Q15" t="n">
-        <v>1272</v>
+        <v>403000</v>
       </c>
       <c r="R15" t="n">
-        <v>-317000</v>
+        <v>-147000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-47000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>대한광통신, 미국 광통신 주가 동향 및 젠슨 황의 광통신 지지 언급. 신고가 기대감.</t>
+          <t>SK하이닉스 ADR 급락 및 연말 목표주가 하향 조정. 자사주 매입 및 소각 관련 논란.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['광통신', '미국', '신고가']</t>
+          <t>['ADR', '목표주가', '자사주']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12810</v>
+        <v>18170</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.54%</t>
+          <t>'-1.94%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.88</v>
+        <v>1.11</v>
       </c>
       <c r="E16" t="n">
-        <v>65</v>
+        <v>127</v>
       </c>
       <c r="F16" t="n">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="G16" t="n">
-        <v>147</v>
+        <v>741</v>
       </c>
       <c r="H16" t="n">
-        <v>1.42</v>
+        <v>4.92</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,38 +1883,38 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>13010</v>
+        <v>18530</v>
       </c>
       <c r="K16" t="n">
-        <v>12330</v>
+        <v>18950</v>
       </c>
       <c r="L16" t="n">
-        <v>13560</v>
+        <v>19870</v>
       </c>
       <c r="M16" t="n">
-        <v>12260</v>
+        <v>18160</v>
       </c>
       <c r="N16" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="O16" t="n">
+        <v>234436472510</v>
+      </c>
+      <c r="P16" t="n">
+        <v>31500</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1272</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-317000</v>
+      </c>
+      <c r="S16" t="n">
         <v>0</v>
       </c>
-      <c r="O16" t="n">
-        <v>32136208105</v>
-      </c>
-      <c r="P16" t="n">
-        <v>22250</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>6000</v>
-      </c>
-      <c r="R16" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3000</v>
-      </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>기타 법인의 자사주 매집과 신규 상장 물량 부담 속에서의 주가 움직임. 유증 물량 소화 과정 및 주가 조작 의혹 제기.</t>
+          <t>대한광통신, 미국 광통신 주가 동향 및 젠슨 황의 광통신 지지 언급. 신고가 기대감.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['자사주', '유상증자', '주가조작']</t>
+          <t>['광통신', '미국', '신고가']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>46600</v>
+        <v>46350</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.69%</t>
+          <t>'-2.22%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.02</v>
       </c>
       <c r="E17" t="n">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F17" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G17" t="n">
-        <v>1576</v>
+        <v>1622</v>
       </c>
       <c r="H17" t="n">
         <v>14.12</v>
@@ -1990,7 +1990,7 @@
         <v>14.1</v>
       </c>
       <c r="O17" t="n">
-        <v>28145221675</v>
+        <v>28704725025</v>
       </c>
       <c r="P17" t="n">
         <v>69200</v>
@@ -2035,31 +2035,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6740</v>
+        <v>12720</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-3.44%</t>
+          <t>'-2.23%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.77</v>
+        <v>1.88</v>
       </c>
       <c r="E18" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F18" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G18" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1</v>
+        <v>1.42</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,47 +2067,47 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>6980</v>
+        <v>13010</v>
       </c>
       <c r="K18" t="n">
-        <v>7000</v>
+        <v>12330</v>
       </c>
       <c r="L18" t="n">
-        <v>7240</v>
+        <v>13560</v>
       </c>
       <c r="M18" t="n">
-        <v>6580</v>
+        <v>12260</v>
       </c>
       <c r="N18" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>39686889600</v>
+        <v>32892471235</v>
       </c>
       <c r="P18" t="n">
-        <v>11370</v>
+        <v>22250</v>
       </c>
       <c r="Q18" t="n">
-        <v>3300</v>
+        <v>6000</v>
       </c>
       <c r="R18" t="n">
-        <v>-37000</v>
+        <v>-100000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>아톤, 망분리 완화 및 금융권 공략 관련 언급. 라온시큐어와 비교되며 기대감 형성.</t>
+          <t>기타법인 자사주 매집, 비만치료제 개발 언급 있으나 유증 및 신주 상장 물량 부담 존재. 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['보안', '망분리', '금융권']</t>
+          <t>['유증', '신주상장', '자사주매집']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>30450</v>
+        <v>30300</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-4.09%</t>
+          <t>'-4.57%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F19" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G19" t="n">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="H19" t="n">
         <v>10.78</v>
@@ -2168,13 +2168,13 @@
         <v>32850</v>
       </c>
       <c r="M19" t="n">
-        <v>30300</v>
+        <v>30200</v>
       </c>
       <c r="N19" t="n">
         <v>10.77</v>
       </c>
       <c r="O19" t="n">
-        <v>68700702275</v>
+        <v>72426257950</v>
       </c>
       <c r="P19" t="n">
         <v>75900</v>
@@ -2213,6 +2213,98 @@
       <c r="Z19" t="inlineStr">
         <is>
           <t>001440</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>아톤</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>6650</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>'-4.73%</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="E20" t="n">
+        <v>50</v>
+      </c>
+      <c r="F20" t="n">
+        <v>36</v>
+      </c>
+      <c r="G20" t="n">
+        <v>159</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>6980</v>
+      </c>
+      <c r="K20" t="n">
+        <v>7000</v>
+      </c>
+      <c r="L20" t="n">
+        <v>7240</v>
+      </c>
+      <c r="M20" t="n">
+        <v>6580</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="O20" t="n">
+        <v>40404960005</v>
+      </c>
+      <c r="P20" t="n">
+        <v>11370</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3300</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-37000</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>망분리 완화 및 금융권 공략 관련 뉴스. 라온시큐어 등 타 보안주 대비 주가 흐름 분석.</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>['망분리', '금융권', '보안주']</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>158430</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261007_10.xlsx
+++ b/data/trending_integrated_20261007_10.xlsx
@@ -578,13 +578,13 @@
         <v>-0.08</v>
       </c>
       <c r="E2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" t="n">
         <v>3.27</v>
@@ -610,7 +610,7 @@
         <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>26002645104</v>
+        <v>26092485504</v>
       </c>
       <c r="P2" t="n">
         <v>5470</v>
@@ -626,12 +626,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>흑사병 테마 치료제 관련 기대감 상승. FDA 언급 및 다수 관련주 동반 강세.</t>
+          <t>흑사병 테마 관련 뉴스 및 종근당바이오, 그린생명과학, 녹십자엠에스 등 연관주 언급. FDA 비상선언 및 공중파 보도 내용 포함. 최대 수혜 기대감.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>제이앤티씨</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26550</v>
+        <v>7820</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.69%</t>
+          <t>'+15.85%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4</v>
+        <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="G3" t="n">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="H3" t="n">
-        <v>2.82</v>
+        <v>5.12</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>22950</v>
+        <v>6750</v>
       </c>
       <c r="K3" t="n">
-        <v>26200</v>
+        <v>6710</v>
       </c>
       <c r="L3" t="n">
-        <v>27600</v>
+        <v>8310</v>
       </c>
       <c r="M3" t="n">
-        <v>25550</v>
+        <v>6690</v>
       </c>
       <c r="N3" t="n">
-        <v>2.42</v>
+        <v>5.14</v>
       </c>
       <c r="O3" t="n">
-        <v>78489888175</v>
+        <v>48199216885</v>
       </c>
       <c r="P3" t="n">
-        <v>30100</v>
+        <v>23500</v>
       </c>
       <c r="Q3" t="n">
-        <v>11140</v>
+        <v>2890</v>
       </c>
       <c r="R3" t="n">
-        <v>158000</v>
+        <v>-226000</v>
       </c>
       <c r="S3" t="n">
-        <v>-205000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>유리 기술력을 바탕으로 한 신규 사업 기대감 및 주포 세력의 움직임. 유상증자 이슈 속에서도 단기 급등 가능성 언급.</t>
+          <t>정부의 용적률 상향 및 그린벨트 해제 관련 뉴스 언급. 성수 메가프로젝트 및 건설 기초 소재 대장주로서의 위치 강조. 10만원 목표가 제시.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['유리기판', '주포', '유상증자']</t>
+          <t>['용적률', '그린벨트', '건설']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>제이앤티씨</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7710</v>
+        <v>26450</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.22%</t>
+          <t>'+15.25%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.02</v>
+        <v>0.4</v>
       </c>
       <c r="E4" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F4" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="H4" t="n">
-        <v>5.12</v>
+        <v>2.82</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>6750</v>
+        <v>22950</v>
       </c>
       <c r="K4" t="n">
-        <v>6710</v>
+        <v>26200</v>
       </c>
       <c r="L4" t="n">
-        <v>8310</v>
+        <v>27600</v>
       </c>
       <c r="M4" t="n">
-        <v>6690</v>
+        <v>25550</v>
       </c>
       <c r="N4" t="n">
-        <v>5.14</v>
+        <v>2.42</v>
       </c>
       <c r="O4" t="n">
-        <v>44792138445</v>
+        <v>79844397975</v>
       </c>
       <c r="P4" t="n">
-        <v>23500</v>
+        <v>30100</v>
       </c>
       <c r="Q4" t="n">
-        <v>2890</v>
+        <v>11140</v>
       </c>
       <c r="R4" t="n">
-        <v>-226000</v>
+        <v>158000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-205000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정부의 용적률 상향 및 그린벨트 해제 검토 발표에 따른 건설 기대감. 대형 프로젝트 참여 가능성 언급.</t>
+          <t>유리 기술력 기반의 브로드컴, 인텔 뚫기 기대감. 주포 2천억 유입 및 3만원 돌파 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['용적률', '그린벨트', '건설']</t>
+          <t>['유리기판', '주포', 'IR']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>204270</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16900</v>
+        <v>13790</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.65%</t>
+          <t>'+11.84%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.98</v>
+        <v>0.31</v>
       </c>
       <c r="E5" t="n">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="F5" t="n">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>151</v>
+        <v>69</v>
       </c>
       <c r="H5" t="n">
-        <v>2.37</v>
+        <v>0.79</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>14870</v>
+        <v>12330</v>
       </c>
       <c r="K5" t="n">
-        <v>15480</v>
+        <v>12580</v>
       </c>
       <c r="L5" t="n">
-        <v>17590</v>
+        <v>14090</v>
       </c>
       <c r="M5" t="n">
-        <v>14600</v>
+        <v>12300</v>
       </c>
       <c r="N5" t="n">
-        <v>1.39</v>
+        <v>0.48</v>
       </c>
       <c r="O5" t="n">
-        <v>190350336615</v>
+        <v>114805441830</v>
       </c>
       <c r="P5" t="n">
-        <v>17590</v>
+        <v>20850</v>
       </c>
       <c r="Q5" t="n">
-        <v>6320</v>
+        <v>4020</v>
       </c>
       <c r="R5" t="n">
-        <v>-91000</v>
+        <v>-5000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>개인정보 유출 및 해킹 관련 이슈 부각으로 인한 보안주 강세. 라온의 양자보안 기술력 언급.</t>
+          <t>한화파워 가스터빈 블레이드 납품 개시 및 원전, 데이터센터 관련 사업 언급. 14,200원 돌파 시 급등 예상 및 텐버거 기대감 표시. 거래량 증가 및 손바뀜 확인.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['개인정보 유출', '보안주', '양자보안']</t>
+          <t>['가스터빈', '원전', '납품']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13740</v>
+        <v>16420</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.44%</t>
+          <t>'+10.42%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.31</v>
+        <v>0.98</v>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="F6" t="n">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="G6" t="n">
-        <v>55</v>
+        <v>161</v>
       </c>
       <c r="H6" t="n">
-        <v>0.79</v>
+        <v>2.37</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>12330</v>
+        <v>14870</v>
       </c>
       <c r="K6" t="n">
-        <v>12580</v>
+        <v>15480</v>
       </c>
       <c r="L6" t="n">
-        <v>13830</v>
+        <v>17590</v>
       </c>
       <c r="M6" t="n">
-        <v>12300</v>
+        <v>14600</v>
       </c>
       <c r="N6" t="n">
-        <v>0.48</v>
+        <v>1.39</v>
       </c>
       <c r="O6" t="n">
-        <v>96751679010</v>
+        <v>198207377345</v>
       </c>
       <c r="P6" t="n">
-        <v>20850</v>
+        <v>17590</v>
       </c>
       <c r="Q6" t="n">
-        <v>4020</v>
+        <v>6320</v>
       </c>
       <c r="R6" t="n">
-        <v>-5000</v>
+        <v>-91000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 가스발전향 가스터빈 블레이드 독점 공급 계약 뉴스. 한화파워 납품 개시 사실 기반 긍정적 전망.</t>
+          <t>개인정보 유출 및 해킹 관련 이슈 부각으로 인한 보안주 강세. 라온의 양자보안 기술력 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['가스터빈', '블레이드', '독점 공급']</t>
+          <t>['개인정보 유출', '보안주', '양자보안']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,86 +1016,86 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10650</v>
+        <v>2625</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+10.13%</t>
+          <t>'+10.06%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.17</v>
+        <v>-0.29</v>
       </c>
       <c r="E7" t="n">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="F7" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="G7" t="n">
-        <v>266</v>
+        <v>58</v>
       </c>
       <c r="H7" t="n">
-        <v>5.01</v>
+        <v>0.82</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>9670</v>
+        <v>2385</v>
       </c>
       <c r="K7" t="n">
-        <v>11020</v>
+        <v>2510</v>
       </c>
       <c r="L7" t="n">
-        <v>11030</v>
+        <v>2900</v>
       </c>
       <c r="M7" t="n">
-        <v>10300</v>
+        <v>2505</v>
       </c>
       <c r="N7" t="n">
-        <v>4.84</v>
+        <v>1.11</v>
       </c>
       <c r="O7" t="n">
-        <v>14175465905</v>
+        <v>8198936754</v>
       </c>
       <c r="P7" t="n">
-        <v>15900</v>
+        <v>4760</v>
       </c>
       <c r="Q7" t="n">
-        <v>6310</v>
+        <v>973</v>
       </c>
       <c r="R7" t="n">
-        <v>-216000</v>
+        <v>-43000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>신풍제약, 다양한 질병 테마주로 언급되나, 흑사병 관련 뉴스와 연계된 기대감 위주.</t>
+          <t>바이오 섹터 전반의 부진 속에서의 기술적 반등 시도. 유상증자 관련 지분 매각 이슈.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['테마주', '흑사병', '백신']</t>
+          <t>['바이오', '유상증자', '기술적 반등']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,86 +1108,86 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>299660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2625</v>
+        <v>10640</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+10.06%</t>
+          <t>'+10.03%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.29</v>
+        <v>0.17</v>
       </c>
       <c r="E8" t="n">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="F8" t="n">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="G8" t="n">
-        <v>57</v>
+        <v>276</v>
       </c>
       <c r="H8" t="n">
-        <v>0.82</v>
+        <v>5.01</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>2385</v>
+        <v>9670</v>
       </c>
       <c r="K8" t="n">
-        <v>2510</v>
+        <v>11020</v>
       </c>
       <c r="L8" t="n">
-        <v>2900</v>
+        <v>11030</v>
       </c>
       <c r="M8" t="n">
-        <v>2505</v>
+        <v>10300</v>
       </c>
       <c r="N8" t="n">
-        <v>1.11</v>
+        <v>4.84</v>
       </c>
       <c r="O8" t="n">
-        <v>8144983854</v>
+        <v>14661688785</v>
       </c>
       <c r="P8" t="n">
-        <v>4760</v>
+        <v>15900</v>
       </c>
       <c r="Q8" t="n">
-        <v>973</v>
+        <v>6310</v>
       </c>
       <c r="R8" t="n">
-        <v>-43000</v>
+        <v>-216000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>바이오 섹터 전반의 부진 속에서의 기술적 반등 시도. 유상증자 관련 지분 매각 이슈.</t>
+          <t>폐렴성 페스트, 에볼라 등 전염병 테마 관련 언급. 러시아 페스트 연구소 관련 뉴스 및 항생제 치료 가능성 언급. 일부 긍정적 기대감 있으나 신중론도 존재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['바이오', '유상증자', '기술적 반등']</t>
+          <t>['전염병', '페스트', '테마주']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>299660</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
@@ -1222,13 +1222,13 @@
         <v>3.32</v>
       </c>
       <c r="E9" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F9" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G9" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H9" t="n">
         <v>4.72</v>
@@ -1254,7 +1254,7 @@
         <v>1.4</v>
       </c>
       <c r="O9" t="n">
-        <v>167118025095</v>
+        <v>170031993220</v>
       </c>
       <c r="P9" t="n">
         <v>8100</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>기타법인의 자사주 매집 및 2200억 규모 수주 계약 기대감. 미국 시장 호조에 따른 긍정적 전망.</t>
+          <t>기타법인의 자사주 매집 및 2200억 규모 수주 계약 공시 임박설 언급. 미국 증시 흐름과 연관하여 상승 기대감 표시. JP모건 순매수 확인.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['자사주 매집', '수주 계약', '미국 시장']</t>
+          <t>['자사주', '수주', '공시']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>272750</v>
+        <v>271750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.28%</t>
+          <t>'-0.09%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="G10" t="n">
-        <v>1860</v>
+        <v>1723</v>
       </c>
       <c r="H10" t="n">
         <v>46.37</v>
@@ -1346,7 +1346,7 @@
         <v>46.41</v>
       </c>
       <c r="O10" t="n">
-        <v>1882029395500</v>
+        <v>1976927736000</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>총 영업이익 대비 낮은 주가에 대한 불만 표출. 정치적 이슈와 기관/연기금 매도에 대한 부정적 언급.</t>
+          <t>반도체 노조 관련 부정적 기사 속에서 주가 부진에 대한 불만 제기. 일부 긍정적 언급 있으나 전반적으로 부정적 분위기.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['영업이익', '주가', '기관']</t>
+          <t>['반도체', '노조', '주가']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>81600</v>
+        <v>81400</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'-0.12%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.03</v>
       </c>
       <c r="E11" t="n">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="F11" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G11" t="n">
-        <v>627</v>
+        <v>637</v>
       </c>
       <c r="H11" t="n">
         <v>22.59</v>
@@ -1432,13 +1432,13 @@
         <v>84300</v>
       </c>
       <c r="M11" t="n">
-        <v>81500</v>
+        <v>81400</v>
       </c>
       <c r="N11" t="n">
         <v>22.56</v>
       </c>
       <c r="O11" t="n">
-        <v>96519610800</v>
+        <v>99803577850</v>
       </c>
       <c r="P11" t="n">
         <v>139200</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>구글의 미국 최대 원전기업과 전력구매 계약 체결 소식을 바탕으로 미국 원전주 급등에 따른 동반 상승 기대감 고조. 공매도 세력과의 전쟁 언급.</t>
+          <t>구글-컨스텔레이션 3.6GW 전력구매 계약 뉴스 기반 원전주 급등 기대. 웨스팅하우스 계약 체결 공시 가능성 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['미국 원전', '전력구매 계약', '공매도']</t>
+          <t>['원전주', '전력구매계약', '공시']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,70 +1483,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17640</v>
+        <v>239250</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.62%</t>
+          <t>'-0.73%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.11</v>
+        <v>0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>47</v>
+        <v>139</v>
       </c>
       <c r="F12" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="G12" t="n">
-        <v>234</v>
+        <v>712</v>
       </c>
       <c r="H12" t="n">
-        <v>9.5</v>
+        <v>4.12</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>17750</v>
+        <v>241000</v>
       </c>
       <c r="K12" t="n">
-        <v>17970</v>
+        <v>253000</v>
       </c>
       <c r="L12" t="n">
-        <v>18030</v>
+        <v>257000</v>
       </c>
       <c r="M12" t="n">
-        <v>17610</v>
+        <v>235000</v>
       </c>
       <c r="N12" t="n">
-        <v>9.390000000000001</v>
+        <v>4.08</v>
       </c>
       <c r="O12" t="n">
-        <v>31459961060</v>
+        <v>69238565250</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>1233000</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>120000</v>
       </c>
       <c r="R12" t="n">
-        <v>-95000</v>
+        <v>-43000</v>
       </c>
       <c r="S12" t="n">
-        <v>-29000</v>
+        <v>2000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>대우건설, 수주 목표 및 미국 원전 건설 분위기 긍정적 언급. 주주 호소 글 다수, 객관적 분석은 부족.</t>
+          <t>경구용 인슐린 10조원대 L/O 예상 및 캐나다, 독일 건 터짐 기대감. 외인 공매도 숏커버링으로 인한 발악 및 거래량 동반 상승.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['수주', '원전', '주주']</t>
+          <t>['공매도', 'L/O', '거래량']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13250</v>
+        <v>17610</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.05%</t>
+          <t>'-0.79%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="E13" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F13" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G13" t="n">
-        <v>66</v>
+        <v>244</v>
       </c>
       <c r="H13" t="n">
-        <v>3.18</v>
+        <v>9.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>13390</v>
+        <v>17750</v>
       </c>
       <c r="K13" t="n">
-        <v>13770</v>
+        <v>17970</v>
       </c>
       <c r="L13" t="n">
-        <v>13830</v>
+        <v>18030</v>
       </c>
       <c r="M13" t="n">
-        <v>13210</v>
+        <v>17610</v>
       </c>
       <c r="N13" t="n">
-        <v>3.12</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>22065703535</v>
+        <v>32340547590</v>
       </c>
       <c r="P13" t="n">
-        <v>20300</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>3020</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>-255000</v>
+        <v>-95000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-29000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>최근 주가 하락 및 박스권 흐름에 대한 답답함 표출. 공매도 및 외국인 매도에 대한 의심.</t>
+          <t>올해 수주 목표 27조 및 미국 원전 건설 관련 긍정적 분위기 언급. 싱가포르 수상 및 미국 원전 수주 기대감. 주주들에게 호소하는 내용 다수 포함.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['전선주', '박스권', '공매도']</t>
+          <t>['수주', '원전', '건설']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,86 +1660,86 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>238000</v>
+        <v>13240</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.24%</t>
+          <t>'-1.12%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>134</v>
+        <v>40</v>
       </c>
       <c r="F14" t="n">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="G14" t="n">
-        <v>691</v>
+        <v>66</v>
       </c>
       <c r="H14" t="n">
-        <v>4.12</v>
+        <v>3.18</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>241000</v>
+        <v>13390</v>
       </c>
       <c r="K14" t="n">
-        <v>253000</v>
+        <v>13770</v>
       </c>
       <c r="L14" t="n">
-        <v>257000</v>
+        <v>13830</v>
       </c>
       <c r="M14" t="n">
-        <v>235000</v>
+        <v>13210</v>
       </c>
       <c r="N14" t="n">
-        <v>4.08</v>
+        <v>3.12</v>
       </c>
       <c r="O14" t="n">
-        <v>68194232000</v>
+        <v>22253739050</v>
       </c>
       <c r="P14" t="n">
-        <v>1233000</v>
+        <v>20300</v>
       </c>
       <c r="Q14" t="n">
-        <v>120000</v>
+        <v>3020</v>
       </c>
       <c r="R14" t="n">
-        <v>-43000</v>
+        <v>-255000</v>
       </c>
       <c r="S14" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>경구용 인슐린 10조원대 LO 예상 및 캐나다/독일 관련 뉴스 기대감 형성. 외국인 숏커버링 추정 수급 동향 관찰.</t>
+          <t>최근 주가 하락 및 박스권 흐름에 대한 답답함 표출. 공매도 및 외국인 매도에 대한 의심.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['경구용 인슐린', '공매도', '숏커버링']</t>
+          <t>['전선주', '박스권', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1745000</v>
+        <v>1739000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.58%</t>
+          <t>'-1.92%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="G15" t="n">
-        <v>1745</v>
+        <v>1708</v>
       </c>
       <c r="H15" t="n">
         <v>49.71</v>
@@ -1806,7 +1806,7 @@
         <v>49.76</v>
       </c>
       <c r="O15" t="n">
-        <v>1823028353500</v>
+        <v>1919028556000</v>
       </c>
       <c r="P15" t="n">
         <v>2987000</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>SK하이닉스 ADR 급락 및 연말 목표주가 하향 조정. 자사주 매입 및 소각 관련 논란.</t>
+          <t>미국 시장 폭락 및 ADR 급락 영향으로 하이닉스 목표 주가 400에도 불구하고 하락세 전망. 자사주 매입 꼼수 및 연기금 매도 지적.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['ADR', '목표주가', '자사주']</t>
+          <t>['ADR', '자사주', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18170</v>
+        <v>18160</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.94%</t>
+          <t>'-2.00%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1.11</v>
       </c>
       <c r="E16" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F16" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G16" t="n">
-        <v>741</v>
+        <v>764</v>
       </c>
       <c r="H16" t="n">
         <v>4.92</v>
@@ -1892,13 +1892,13 @@
         <v>19870</v>
       </c>
       <c r="M16" t="n">
-        <v>18160</v>
+        <v>18150</v>
       </c>
       <c r="N16" t="n">
         <v>3.81</v>
       </c>
       <c r="O16" t="n">
-        <v>234436472510</v>
+        <v>237672752095</v>
       </c>
       <c r="P16" t="n">
         <v>31500</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>대한광통신, 미국 광통신 주가 동향 및 젠슨 황의 광통신 지지 언급. 신고가 기대감.</t>
+          <t>미국 광통신 주가 상승 및 젠슨 황의 광통신 지지 언급. 19,870원 안착 및 2만원 돌파 기대감 표시. 일부 고점 매도 의견 존재.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['광통신', '미국', '신고가']</t>
+          <t>['광통신', '모멘텀', '주가']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1943,31 +1943,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>46350</v>
+        <v>12700</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.22%</t>
+          <t>'-2.38%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.02</v>
+        <v>1.88</v>
       </c>
       <c r="E17" t="n">
-        <v>247</v>
+        <v>65</v>
       </c>
       <c r="F17" t="n">
-        <v>154</v>
+        <v>52</v>
       </c>
       <c r="G17" t="n">
-        <v>1622</v>
+        <v>147</v>
       </c>
       <c r="H17" t="n">
-        <v>14.12</v>
+        <v>1.42</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,47 +1975,47 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>47400</v>
+        <v>13010</v>
       </c>
       <c r="K17" t="n">
-        <v>46350</v>
+        <v>12330</v>
       </c>
       <c r="L17" t="n">
-        <v>47850</v>
+        <v>13560</v>
       </c>
       <c r="M17" t="n">
-        <v>45650</v>
+        <v>12260</v>
       </c>
       <c r="N17" t="n">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>28704725025</v>
+        <v>33194886425</v>
       </c>
       <c r="P17" t="n">
-        <v>69200</v>
+        <v>22250</v>
       </c>
       <c r="Q17" t="n">
-        <v>24150</v>
+        <v>6000</v>
       </c>
       <c r="R17" t="n">
-        <v>5000</v>
+        <v>-100000</v>
       </c>
       <c r="S17" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>FDA 승인 가능성 90% 이상 언급 및 시총 100조원 목표 제시. 공매도 세력에 대한 비판과 함께 대세 우상향 전망.</t>
+          <t>기타법인 자사주 매집, 비만치료제 개발 언급 있으나 유증 및 신주 상장 물량 부담 존재. 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['FDA 승인', '공매도', '대세 우상향']</t>
+          <t>['유증', '신주상장', '자사주매집']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12720</v>
+        <v>46200</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.23%</t>
+          <t>'-2.53%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.88</v>
+        <v>0.02</v>
       </c>
       <c r="E18" t="n">
-        <v>65</v>
+        <v>248</v>
       </c>
       <c r="F18" t="n">
-        <v>52</v>
+        <v>154</v>
       </c>
       <c r="G18" t="n">
-        <v>146</v>
+        <v>1657</v>
       </c>
       <c r="H18" t="n">
-        <v>1.42</v>
+        <v>14.12</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,47 +2067,47 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>13010</v>
+        <v>47400</v>
       </c>
       <c r="K18" t="n">
-        <v>12330</v>
+        <v>46350</v>
       </c>
       <c r="L18" t="n">
-        <v>13560</v>
+        <v>47850</v>
       </c>
       <c r="M18" t="n">
-        <v>12260</v>
+        <v>45650</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="O18" t="n">
-        <v>32892471235</v>
+        <v>29358703400</v>
       </c>
       <c r="P18" t="n">
-        <v>22250</v>
+        <v>69200</v>
       </c>
       <c r="Q18" t="n">
-        <v>6000</v>
+        <v>24150</v>
       </c>
       <c r="R18" t="n">
-        <v>-100000</v>
+        <v>5000</v>
       </c>
       <c r="S18" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>기타법인 자사주 매집, 비만치료제 개발 언급 있으나 유증 및 신주 상장 물량 부담 존재. 주가 조작 의혹 제기.</t>
+          <t>FDA 승인 가능성 90% 이상 언급 및 시총 100조원 목표 제시. 공매도 세력에 대한 비판과 함께 대세 우상향 전망.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['유증', '신주상장', '자사주매집']</t>
+          <t>['FDA 승인', '공매도', '대세 우상향']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -2142,13 +2142,13 @@
         <v>0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F19" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G19" t="n">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="H19" t="n">
         <v>10.78</v>
@@ -2174,7 +2174,7 @@
         <v>10.77</v>
       </c>
       <c r="O19" t="n">
-        <v>72426257950</v>
+        <v>74043075050</v>
       </c>
       <c r="P19" t="n">
         <v>75900</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>대한전선, 경쟁사(가온전선)와 비교되며 부진한 실적 및 주가 관리 문제 지적. 외인 매도세 언급.</t>
+          <t>가온전선과의 주가 비교하며 실력 및 기술력 차이 언급. 외인 매도세와 주가 하락 지속에 대한 불만 제기. 일부 반등 기대감 있으나 전반적으로 부정적.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['가온전선', '실적', '외인']</t>
+          <t>['주가', '외인', '기술력']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6650</v>
+        <v>6620</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-4.73%</t>
+          <t>'-5.16%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.77</v>
       </c>
       <c r="E20" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F20" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G20" t="n">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="H20" t="n">
         <v>1.1</v>
@@ -2266,7 +2266,7 @@
         <v>1.87</v>
       </c>
       <c r="O20" t="n">
-        <v>40404960005</v>
+        <v>41041291110</v>
       </c>
       <c r="P20" t="n">
         <v>11370</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>망분리 완화 및 금융권 공략 관련 뉴스. 라온시큐어 등 타 보안주 대비 주가 흐름 분석.</t>
+          <t>망분리 완화 관련 금융권 공략 소식 및 3분기 역대급 실적 기대감 언급. 라온시큐어와의 비교 및 보안주로서의 성장 가능성 제시. 시가총액 1조 달성.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['망분리', '금융권', '보안주']</t>
+          <t>['망분리', '보안주', '실적']</t>
         </is>
       </c>
       <c r="X20" t="n">
